--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="1074">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3228,6 +3228,24 @@
   </si>
   <si>
     <t>Prestige Pandemonium</t>
+  </si>
+  <si>
+    <t>Pizza Chef</t>
+  </si>
+  <si>
+    <t>Pasta Maker</t>
+  </si>
+  <si>
+    <t>Breadsticks</t>
+  </si>
+  <si>
+    <t>Spaghetti alla</t>
+  </si>
+  <si>
+    <t>Eternal Aspect</t>
+  </si>
+  <si>
+    <t>Eclipse Eternal Aspect</t>
   </si>
 </sst>
 </file>
@@ -5241,6 +5259,12 @@
       <c r="P31" s="8" t="s">
         <v>994</v>
       </c>
+      <c r="Q31" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>1073</v>
+      </c>
       <c r="T31" s="41"/>
       <c r="U31" s="41"/>
       <c r="V31" s="41"/>
@@ -6164,6 +6188,9 @@
       <c r="G51" s="11" t="s">
         <v>978</v>
       </c>
+      <c r="H51" s="1" t="s">
+        <v>1069</v>
+      </c>
       <c r="T51" s="41"/>
       <c r="U51" s="41"/>
       <c r="V51" s="41"/>
@@ -6217,6 +6244,9 @@
       </c>
       <c r="P52" s="6" t="s">
         <v>173</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>1070</v>
       </c>
       <c r="T52" s="41"/>
       <c r="U52" s="41"/>
@@ -7356,7 +7386,9 @@
       <c r="S76" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="T76" s="41"/>
+      <c r="T76" s="41" t="s">
+        <v>1072</v>
+      </c>
       <c r="U76" s="41"/>
       <c r="V76" s="41"/>
       <c r="W76" s="2"/>
@@ -9623,6 +9655,9 @@
       <c r="L127" s="8" t="s">
         <v>1022</v>
       </c>
+      <c r="M127" s="1" t="s">
+        <v>1068</v>
+      </c>
       <c r="T127" s="41"/>
       <c r="U127" s="41"/>
       <c r="V127" s="41"/>
@@ -10783,6 +10818,9 @@
       </c>
       <c r="H152" s="11" t="s">
         <v>940</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="T152" s="41"/>
       <c r="U152" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2254" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1076">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3246,6 +3246,12 @@
   </si>
   <si>
     <t>Eclipse Eternal Aspect</t>
+  </si>
+  <si>
+    <t>Sinful Shores</t>
+  </si>
+  <si>
+    <t>Prestige Sinful Shores</t>
   </si>
 </sst>
 </file>
@@ -4859,6 +4865,9 @@
       <c r="N22" s="10" t="s">
         <v>893</v>
       </c>
+      <c r="O22" s="1" t="s">
+        <v>1074</v>
+      </c>
       <c r="T22" s="41"/>
       <c r="U22" s="41"/>
       <c r="V22" s="41"/>
@@ -6160,6 +6169,9 @@
       </c>
       <c r="D50" s="10" t="s">
         <v>173</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>1074</v>
       </c>
       <c r="T50" s="41"/>
       <c r="U50" s="41"/>
@@ -7257,6 +7269,9 @@
       </c>
       <c r="O74" s="8" t="s">
         <v>968</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>1075</v>
       </c>
       <c r="T74" s="41"/>
       <c r="U74" s="41"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="1077">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3252,6 +3252,9 @@
   </si>
   <si>
     <t>Prestige Sinful Shores</t>
+  </si>
+  <si>
+    <t>Locke</t>
   </si>
 </sst>
 </file>
@@ -3975,7 +3978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W176"/>
+  <dimension ref="A1:W177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -4267,6 +4270,9 @@
       <c r="E8" s="6" t="s">
         <v>910</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="T8" s="41"/>
       <c r="U8" s="41"/>
       <c r="V8" s="41"/>
@@ -4665,7 +4671,9 @@
       <c r="D17" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="E17" s="45"/>
+      <c r="E17" s="45" t="s">
+        <v>903</v>
+      </c>
       <c r="F17" s="45"/>
       <c r="T17" s="41"/>
       <c r="U17" s="41"/>
@@ -6560,6 +6568,9 @@
       <c r="N58" s="8" t="s">
         <v>278</v>
       </c>
+      <c r="O58" s="1" t="s">
+        <v>903</v>
+      </c>
       <c r="T58" s="41"/>
       <c r="U58" s="41"/>
       <c r="V58" s="41"/>
@@ -7479,53 +7490,22 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F79" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="G79" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B79" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="H79" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="I79" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="J79" s="10" t="s">
-        <v>857</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="M79" s="11" t="s">
-        <v>886</v>
-      </c>
-      <c r="N79" s="8" t="s">
-        <v>895</v>
-      </c>
-      <c r="O79" s="11" t="s">
-        <v>1019</v>
-      </c>
-      <c r="P79" s="7" t="s">
-        <v>1046</v>
-      </c>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="45"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="45"/>
       <c r="T79" s="41"/>
       <c r="U79" s="41"/>
       <c r="V79" s="41"/>
@@ -7533,49 +7513,52 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>503</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>504</v>
+        <v>54</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>272</v>
       </c>
       <c r="J80" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="K80" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="L80" s="13" t="s">
-        <v>858</v>
-      </c>
-      <c r="M80" s="13" t="s">
-        <v>880</v>
-      </c>
-      <c r="N80" s="11" t="s">
-        <v>819</v>
-      </c>
-      <c r="O80" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="L80" s="6" t="s">
         <v>278</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>886</v>
+      </c>
+      <c r="N80" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="O80" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="P80" s="7" t="s">
+        <v>1046</v>
       </c>
       <c r="T80" s="41"/>
       <c r="U80" s="41"/>
@@ -7584,174 +7567,174 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="E81" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="F81" s="13" t="s">
-        <v>507</v>
+        <v>55</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="D81" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>439</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="H81" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="H81" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="I81" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>509</v>
+      <c r="I81" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="J81" s="10" t="s">
+        <v>338</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="L81" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="M81" s="8" t="s">
-        <v>856</v>
-      </c>
-      <c r="N81" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="O81" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="P81" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="Q81" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="R81" s="8" t="s">
-        <v>859</v>
-      </c>
-      <c r="S81" s="9" t="s">
-        <v>893</v>
-      </c>
-      <c r="T81" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="U81" s="47" t="s">
-        <v>906</v>
-      </c>
-      <c r="V81" s="48" t="s">
-        <v>869</v>
-      </c>
-      <c r="W81" s="53" t="s">
-        <v>1043</v>
-      </c>
+      <c r="L81" s="13" t="s">
+        <v>858</v>
+      </c>
+      <c r="M81" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="N81" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="T81" s="41"/>
+      <c r="U81" s="41"/>
+      <c r="V81" s="41"/>
+      <c r="W81" s="2"/>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" s="12" t="s">
-        <v>511</v>
-      </c>
-      <c r="D82" s="13" t="s">
-        <v>512</v>
+        <v>56</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>506</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>513</v>
-      </c>
-      <c r="F82" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="G82" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I82" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>163</v>
+        <v>362</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>509</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="L82" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="M82" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="N82" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="P82" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="T82" s="41"/>
-      <c r="U82" s="41"/>
-      <c r="V82" s="41"/>
-      <c r="W82" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="M82" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="O82" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="P82" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q82" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="R82" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="S82" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="T82" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="U82" s="47" t="s">
+        <v>906</v>
+      </c>
+      <c r="V82" s="48" t="s">
+        <v>869</v>
+      </c>
+      <c r="W82" s="53" t="s">
+        <v>1043</v>
+      </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C83" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="F83" s="13" t="s">
-        <v>520</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="I83" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="K83" s="11" t="s">
-        <v>522</v>
-      </c>
-      <c r="L83" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="M83" s="8" t="s">
-        <v>910</v>
-      </c>
-      <c r="N83" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>1028</v>
+        <v>57</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="L83" s="13" t="s">
+        <v>860</v>
+      </c>
+      <c r="M83" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="P83" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="T83" s="41"/>
       <c r="U83" s="41"/>
@@ -7760,43 +7743,49 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="G84" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>527</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="J84" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>520</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="I84" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="J84" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="K84" s="10" t="s">
-        <v>240</v>
+      <c r="K84" s="11" t="s">
+        <v>522</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>917</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>1056</v>
+        <v>335</v>
+      </c>
+      <c r="M84" s="8" t="s">
+        <v>910</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>1028</v>
       </c>
       <c r="T84" s="41"/>
       <c r="U84" s="41"/>
@@ -7805,61 +7794,43 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="F85" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="G85" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="J85" s="8" t="s">
-        <v>533</v>
+        <v>58</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>521</v>
       </c>
       <c r="K85" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="N85" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="P85" s="13" t="s">
-        <v>869</v>
-      </c>
-      <c r="Q85" s="10" t="s">
-        <v>915</v>
-      </c>
-      <c r="R85" s="10" t="s">
-        <v>947</v>
-      </c>
-      <c r="S85" s="1" t="s">
-        <v>1064</v>
+        <v>240</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>917</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>1056</v>
       </c>
       <c r="T85" s="41"/>
       <c r="U85" s="41"/>
@@ -7868,30 +7839,62 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>896</v>
-      </c>
-      <c r="E86" s="45"/>
-      <c r="F86" s="45"/>
-      <c r="G86" s="45"/>
-      <c r="H86" s="45"/>
-      <c r="I86" s="45"/>
-      <c r="J86" s="45"/>
-      <c r="K86" s="45"/>
-      <c r="L86" s="45"/>
-      <c r="M86" s="45"/>
-      <c r="N86" s="45"/>
-      <c r="O86" s="45"/>
-      <c r="P86" s="45"/>
-      <c r="Q86" s="45"/>
+        <v>59</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="J86" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="K86" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="L86" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="M86" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="N86" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="O86" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="P86" s="13" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q86" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="R86" s="10" t="s">
+        <v>947</v>
+      </c>
+      <c r="S86" s="1" t="s">
+        <v>1064</v>
+      </c>
       <c r="T86" s="41"/>
       <c r="U86" s="41"/>
       <c r="V86" s="41"/>
@@ -7899,20 +7902,30 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C87" s="11" t="s">
-        <v>906</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>439</v>
-      </c>
+        <v>1016</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="E87" s="45"/>
+      <c r="F87" s="45"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="45"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="45"/>
+      <c r="L87" s="45"/>
+      <c r="M87" s="45"/>
+      <c r="N87" s="45"/>
+      <c r="O87" s="45"/>
+      <c r="P87" s="45"/>
+      <c r="Q87" s="45"/>
       <c r="T87" s="41"/>
       <c r="U87" s="41"/>
       <c r="V87" s="41"/>
@@ -7920,183 +7933,141 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>535</v>
+        <v>909</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>906</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>536</v>
+        <v>970</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="G88" s="13" t="s">
-        <v>539</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="K88" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="L88" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="M88" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="N88" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="Q88" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="R88" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="S88" s="11" t="s">
-        <v>903</v>
-      </c>
-      <c r="T88" s="44" t="s">
-        <v>904</v>
-      </c>
-      <c r="U88" s="44" t="s">
-        <v>821</v>
-      </c>
-      <c r="V88" s="44" t="s">
-        <v>976</v>
-      </c>
-      <c r="W88" s="51" t="s">
-        <v>307</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="T88" s="41"/>
+      <c r="U88" s="41"/>
+      <c r="V88" s="41"/>
+      <c r="W88" s="2"/>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>444</v>
+        <v>60</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>537</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="I89" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>808</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>897</v>
+        <v>538</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="M89" s="11" t="s">
-        <v>803</v>
-      </c>
-      <c r="N89" s="10" t="s">
-        <v>1027</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="T89" s="41"/>
-      <c r="U89" s="41"/>
-      <c r="V89" s="41"/>
-      <c r="W89" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q89" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="R89" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="S89" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="T89" s="44" t="s">
+        <v>904</v>
+      </c>
+      <c r="U89" s="44" t="s">
+        <v>821</v>
+      </c>
+      <c r="V89" s="44" t="s">
+        <v>976</v>
+      </c>
+      <c r="W89" s="51" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C90" s="13" t="s">
-        <v>543</v>
+      <c r="C90" s="11" t="s">
+        <v>541</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="E90" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>546</v>
+        <v>177</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>298</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="I90" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>326</v>
+        <v>542</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="J90" s="10" t="s">
+        <v>808</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="L90" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="M90" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="N90" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="O90" s="8" t="s">
-        <v>878</v>
-      </c>
-      <c r="P90" s="7" t="s">
-        <v>877</v>
-      </c>
-      <c r="Q90" s="8" t="s">
-        <v>821</v>
-      </c>
-      <c r="R90" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="S90" s="6" t="s">
-        <v>1047</v>
+        <v>232</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="M90" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>1061</v>
       </c>
       <c r="T90" s="41"/>
       <c r="U90" s="41"/>
@@ -8105,22 +8076,61 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>921</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>920</v>
+        <v>62</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>543</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>1057</v>
+        <v>544</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>545</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="M91" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="N91" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="O91" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="P91" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q91" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="R91" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="S91" s="6" t="s">
+        <v>1047</v>
       </c>
       <c r="T91" s="41"/>
       <c r="U91" s="41"/>
@@ -8129,52 +8139,22 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="E92" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="G92" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="K92" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="L92" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="N92" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="O92" s="8" t="s">
-        <v>898</v>
-      </c>
-      <c r="P92" s="8" t="s">
-        <v>1046</v>
+        <v>921</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="T92" s="41"/>
       <c r="U92" s="41"/>
@@ -8183,49 +8163,52 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>198</v>
+        <v>63</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>550</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>554</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>521</v>
+        <v>551</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>552</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="K93" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="L93" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="K93" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="L93" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="M93" s="10" t="s">
-        <v>884</v>
+      <c r="M93" s="6" t="s">
+        <v>858</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="O93" s="10" t="s">
-        <v>1029</v>
+        <v>276</v>
+      </c>
+      <c r="O93" s="8" t="s">
+        <v>898</v>
+      </c>
+      <c r="P93" s="8" t="s">
+        <v>1046</v>
       </c>
       <c r="T93" s="41"/>
       <c r="U93" s="41"/>
@@ -8234,43 +8217,49 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="D94" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G94" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="I94" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="H94" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>430</v>
-      </c>
       <c r="J94" s="6" t="s">
-        <v>889</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>926</v>
-      </c>
-      <c r="L94" s="8" t="s">
-        <v>950</v>
-      </c>
-      <c r="M94" s="8" t="s">
-        <v>1048</v>
+        <v>556</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>884</v>
+      </c>
+      <c r="N94" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="O94" s="10" t="s">
+        <v>1029</v>
       </c>
       <c r="T94" s="41"/>
       <c r="U94" s="41"/>
@@ -8279,34 +8268,43 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B95" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="F95" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I95" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="G95" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="H95" s="12" t="s">
-        <v>930</v>
-      </c>
-      <c r="I95" s="12" t="s">
-        <v>990</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>1041</v>
+      <c r="J95" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>1048</v>
       </c>
       <c r="T95" s="41"/>
       <c r="U95" s="41"/>
@@ -8315,58 +8313,34 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>198</v>
+        <v>138</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>430</v>
       </c>
       <c r="G96" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="H96" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="K96" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="L96" s="11" t="s">
-        <v>440</v>
-      </c>
-      <c r="M96" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="O96" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="P96" s="13" t="s">
-        <v>911</v>
-      </c>
-      <c r="Q96" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>173</v>
+      <c r="H96" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="J96" s="8" t="s">
+        <v>1041</v>
       </c>
       <c r="T96" s="41"/>
       <c r="U96" s="41"/>
@@ -8375,19 +8349,58 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B97" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>915</v>
+        <v>66</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G97" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="K97" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="O97" s="11" t="s">
+        <v>875</v>
+      </c>
+      <c r="P97" s="13" t="s">
+        <v>911</v>
+      </c>
+      <c r="Q97" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="T97" s="41"/>
       <c r="U97" s="41"/>
@@ -8396,40 +8409,19 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="F98" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="G98" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>566</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>803</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="L98" s="10" t="s">
-        <v>893</v>
+        <v>879</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>915</v>
       </c>
       <c r="T98" s="41"/>
       <c r="U98" s="41"/>
@@ -8438,46 +8430,40 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C99" s="9" t="s">
-        <v>567</v>
+        <v>139</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>563</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>568</v>
+        <v>356</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>570</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>571</v>
-      </c>
-      <c r="H99" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="I99" s="13" t="s">
-        <v>256</v>
+        <v>564</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>565</v>
+      </c>
+      <c r="G99" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>803</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="K99" s="13" t="s">
-        <v>252</v>
+        <v>194</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>903</v>
       </c>
       <c r="L99" s="10" t="s">
-        <v>829</v>
-      </c>
-      <c r="M99" s="10" t="s">
-        <v>927</v>
-      </c>
-      <c r="N99" s="10" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="T99" s="41"/>
       <c r="U99" s="41"/>
@@ -8486,43 +8472,46 @@
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>572</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="G100" s="11" t="s">
-        <v>191</v>
+        <v>67</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>571</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>573</v>
-      </c>
-      <c r="I100" s="10" t="s">
-        <v>192</v>
+        <v>320</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>256</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>800</v>
-      </c>
-      <c r="L100" s="13" t="s">
-        <v>808</v>
+        <v>212</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="L100" s="10" t="s">
+        <v>829</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>177</v>
+        <v>927</v>
+      </c>
+      <c r="N100" s="10" t="s">
+        <v>889</v>
       </c>
       <c r="T100" s="41"/>
       <c r="U100" s="41"/>
@@ -8531,46 +8520,43 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>574</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>575</v>
+        <v>68</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>515</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="H101" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="J101" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="K101" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="L101" s="8" t="s">
-        <v>826</v>
-      </c>
-      <c r="M101" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="N101" s="7" t="s">
-        <v>980</v>
+        <v>572</v>
+      </c>
+      <c r="F101" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H101" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>800</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="T101" s="41"/>
       <c r="U101" s="41"/>
@@ -8579,25 +8565,46 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C102" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>172</v>
+      <c r="C102" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>575</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>953</v>
-      </c>
-      <c r="G102" s="11" t="s">
-        <v>1050</v>
+        <v>576</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="K102" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="M102" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="N102" s="7" t="s">
+        <v>980</v>
       </c>
       <c r="T102" s="41"/>
       <c r="U102" s="41"/>
@@ -8606,49 +8613,25 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B103" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B103" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>579</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="I103" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="J103" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="K103" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="N103" s="10" t="s">
-        <v>966</v>
-      </c>
-      <c r="O103" s="11" t="s">
-        <v>996</v>
+        <v>577</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F103" s="11" t="s">
+        <v>953</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>1050</v>
       </c>
       <c r="T103" s="41"/>
       <c r="U103" s="41"/>
@@ -8657,49 +8640,49 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>583</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>584</v>
+        <v>70</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>579</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>586</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="H104" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="I104" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="K104" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="L104" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="M104" s="10" t="s">
-        <v>326</v>
+        <v>580</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H104" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I104" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="K104" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>863</v>
       </c>
       <c r="N104" s="10" t="s">
-        <v>819</v>
-      </c>
-      <c r="O104" s="10" t="s">
-        <v>432</v>
+        <v>966</v>
+      </c>
+      <c r="O104" s="11" t="s">
+        <v>996</v>
       </c>
       <c r="T104" s="41"/>
       <c r="U104" s="41"/>
@@ -8708,46 +8691,49 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C105" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>834</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="J105" s="13" t="s">
-        <v>920</v>
-      </c>
-      <c r="K105" s="11" t="s">
-        <v>922</v>
+      <c r="C105" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="L105" s="11" t="s">
-        <v>889</v>
-      </c>
-      <c r="M105" s="11" t="s">
-        <v>915</v>
-      </c>
-      <c r="N105" s="11" t="s">
-        <v>980</v>
+        <v>240</v>
+      </c>
+      <c r="M105" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="N105" s="10" t="s">
+        <v>819</v>
+      </c>
+      <c r="O105" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="T105" s="41"/>
       <c r="U105" s="41"/>
@@ -8756,34 +8742,46 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B106" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B106" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="E106" s="11" t="s">
-        <v>864</v>
-      </c>
-      <c r="F106" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="I106" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="J106" s="9" t="s">
-        <v>856</v>
+        <v>590</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="I106" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="K106" s="11" t="s">
+        <v>922</v>
+      </c>
+      <c r="L106" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="M106" s="11" t="s">
+        <v>915</v>
+      </c>
+      <c r="N106" s="11" t="s">
+        <v>980</v>
       </c>
       <c r="T106" s="41"/>
       <c r="U106" s="41"/>
@@ -8792,31 +8790,34 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>593</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>183</v>
+      <c r="C107" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E107" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="F107" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>931</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>856</v>
       </c>
       <c r="T107" s="41"/>
       <c r="U107" s="41"/>
@@ -8825,46 +8826,31 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>594</v>
+      <c r="C108" s="8" t="s">
+        <v>591</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E108" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="G108" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="H108" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="H108" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="I108" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>934</v>
-      </c>
-      <c r="L108" s="9" t="s">
-        <v>942</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>943</v>
-      </c>
-      <c r="N108" s="11" t="s">
-        <v>274</v>
+      <c r="I108" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="T108" s="41"/>
       <c r="U108" s="41"/>
@@ -8873,43 +8859,46 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C109" s="13" t="s">
-        <v>595</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>596</v>
+        <v>75</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>597</v>
-      </c>
-      <c r="F109" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="G109" s="13" t="s">
-        <v>598</v>
-      </c>
-      <c r="H109" s="11" t="s">
-        <v>426</v>
-      </c>
-      <c r="I109" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="J109" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="K109" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="L109" s="13" t="s">
-        <v>240</v>
+        <v>337</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I109" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="J109" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="K109" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="L109" s="9" t="s">
+        <v>942</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>956</v>
+        <v>943</v>
+      </c>
+      <c r="N109" s="11" t="s">
+        <v>274</v>
       </c>
       <c r="T109" s="41"/>
       <c r="U109" s="41"/>
@@ -8918,25 +8907,43 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B110" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C110" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G110" s="8" t="s">
-        <v>975</v>
+      <c r="C110" s="13" t="s">
+        <v>595</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="E110" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="G110" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="I110" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="J110" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="K110" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="L110" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="M110" s="10" t="s">
+        <v>956</v>
       </c>
       <c r="T110" s="41"/>
       <c r="U110" s="41"/>
@@ -8945,22 +8952,25 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>1022</v>
+        <v>77</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>975</v>
       </c>
       <c r="T111" s="41"/>
       <c r="U111" s="41"/>
@@ -8969,25 +8979,22 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="B112" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>839</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>889</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>931</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>932</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>1014</v>
+        <v>141</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="F112" s="11" t="s">
+        <v>1022</v>
       </c>
       <c r="T112" s="41"/>
       <c r="U112" s="41"/>
@@ -8996,55 +9003,25 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>142</v>
+        <v>838</v>
       </c>
       <c r="B113" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C113" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="E113" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="F113" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="G113" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="H113" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="J113" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="K113" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="L113" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="M113" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="N113" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="O113" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>933</v>
-      </c>
-      <c r="Q113" s="11" t="s">
-        <v>915</v>
+      <c r="C113" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>931</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>932</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>1014</v>
       </c>
       <c r="T113" s="41"/>
       <c r="U113" s="41"/>
@@ -9053,34 +9030,55 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>604</v>
+        <v>142</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C114" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>599</v>
       </c>
       <c r="E114" s="10" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G114" s="12" t="s">
-        <v>606</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="I114" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="J114" s="10" t="s">
-        <v>930</v>
+        <v>601</v>
+      </c>
+      <c r="G114" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="H114" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="I114" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="K114" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="N114" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="O114" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="Q114" s="11" t="s">
+        <v>915</v>
       </c>
       <c r="T114" s="41"/>
       <c r="U114" s="41"/>
@@ -9089,58 +9087,34 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B115" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="F115" s="10" t="s">
-        <v>961</v>
-      </c>
-      <c r="G115" s="11" t="s">
-        <v>610</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="I115" s="10" t="s">
-        <v>967</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="K115" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="L115" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="M115" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="N115" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="O115" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="F115" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="G115" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="I115" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="P115" s="11" t="s">
-        <v>830</v>
-      </c>
-      <c r="Q115" s="9" t="s">
-        <v>903</v>
-      </c>
-      <c r="R115" s="8" t="s">
-        <v>944</v>
+      <c r="J115" s="10" t="s">
+        <v>930</v>
       </c>
       <c r="T115" s="41"/>
       <c r="U115" s="41"/>
@@ -9149,28 +9123,58 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="B116" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C116" s="11" t="s">
-        <v>612</v>
+      <c r="C116" s="10" t="s">
+        <v>607</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="E116" s="9" t="s">
-        <v>222</v>
+        <v>608</v>
+      </c>
+      <c r="E116" s="11" t="s">
+        <v>609</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>614</v>
-      </c>
-      <c r="G116" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="H116" s="13" t="s">
-        <v>819</v>
+        <v>961</v>
+      </c>
+      <c r="G116" s="11" t="s">
+        <v>610</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>967</v>
+      </c>
+      <c r="J116" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="K116" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="M116" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="N116" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="O116" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="P116" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="Q116" s="9" t="s">
+        <v>903</v>
+      </c>
+      <c r="R116" s="8" t="s">
+        <v>944</v>
       </c>
       <c r="T116" s="41"/>
       <c r="U116" s="41"/>
@@ -9179,52 +9183,28 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>616</v>
+        <v>143</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>613</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="G117" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="H117" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="I117" s="13" t="s">
-        <v>620</v>
-      </c>
-      <c r="J117" s="13" t="s">
-        <v>621</v>
-      </c>
-      <c r="K117" s="11" t="s">
-        <v>622</v>
-      </c>
-      <c r="L117" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="M117" s="8" t="s">
-        <v>962</v>
-      </c>
-      <c r="N117" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="O117" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="P117" s="6" t="s">
-        <v>161</v>
+        <v>222</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="G117" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H117" s="13" t="s">
+        <v>819</v>
       </c>
       <c r="T117" s="41"/>
       <c r="U117" s="41"/>
@@ -9233,28 +9213,52 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B118" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>232</v>
+        <v>80</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>617</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>920</v>
-      </c>
-      <c r="G118" s="8" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H118" s="10" t="s">
-        <v>393</v>
+        <v>618</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="I118" s="13" t="s">
+        <v>620</v>
+      </c>
+      <c r="J118" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="K118" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="L118" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="M118" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="N118" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="T118" s="41"/>
       <c r="U118" s="41"/>
@@ -9263,49 +9267,28 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>624</v>
-      </c>
-      <c r="E119" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>625</v>
-      </c>
-      <c r="G119" s="11" t="s">
-        <v>626</v>
-      </c>
-      <c r="H119" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="I119" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="J119" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="K119" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="L119" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="M119" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="N119" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>1062</v>
+        <v>144</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>393</v>
       </c>
       <c r="T119" s="41"/>
       <c r="U119" s="41"/>
@@ -9314,43 +9297,49 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="B120" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D120" s="9" t="s">
-        <v>864</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="F120" s="13" t="s">
+      <c r="C120" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="G120" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="H120" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="I120" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="J120" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="L120" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="G120" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>866</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K120" s="8" t="s">
-        <v>895</v>
-      </c>
-      <c r="L120" s="6" t="s">
-        <v>1019</v>
-      </c>
-      <c r="M120" s="1" t="s">
-        <v>1057</v>
+      <c r="M120" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="N120" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>1062</v>
       </c>
       <c r="T120" s="41"/>
       <c r="U120" s="41"/>
@@ -9359,40 +9348,43 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B121" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>796</v>
+        <v>184</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>797</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>806</v>
+        <v>864</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="F121" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>875</v>
-      </c>
-      <c r="H121" s="8" t="s">
-        <v>876</v>
-      </c>
-      <c r="I121" s="5" t="s">
-        <v>906</v>
-      </c>
-      <c r="J121" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="I121" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="J121" s="10" t="s">
         <v>170</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>974</v>
+        <v>895</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>432</v>
+        <v>1019</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="T121" s="41"/>
       <c r="U121" s="41"/>
@@ -9401,40 +9393,40 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C122" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="E122" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="G122" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>797</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>875</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="J122" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="K122" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="L122" s="6" t="s">
         <v>432</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="I122" s="10" t="s">
-        <v>920</v>
-      </c>
-      <c r="J122" s="11" t="s">
-        <v>935</v>
-      </c>
-      <c r="K122" s="8" t="s">
-        <v>1013</v>
-      </c>
-      <c r="L122" s="9" t="s">
-        <v>1032</v>
       </c>
       <c r="T122" s="41"/>
       <c r="U122" s="41"/>
@@ -9443,58 +9435,40 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>629</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>630</v>
-      </c>
-      <c r="E123" s="13" t="s">
-        <v>631</v>
-      </c>
-      <c r="F123" s="12" t="s">
-        <v>568</v>
+        <v>83</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>273</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>632</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="J123" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="K123" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="L123" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="M123" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="N123" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I123" s="10" t="s">
         <v>920</v>
       </c>
-      <c r="O123" s="13" t="s">
-        <v>922</v>
-      </c>
-      <c r="P123" s="10" t="s">
-        <v>889</v>
-      </c>
-      <c r="Q123" s="12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>1067</v>
+      <c r="J123" s="11" t="s">
+        <v>935</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>1032</v>
       </c>
       <c r="T123" s="41"/>
       <c r="U123" s="41"/>
@@ -9503,46 +9477,58 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B124" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C124" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="E124" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="H124" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="J124" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K124" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="L124" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="M124" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="N124" s="6" t="s">
-        <v>910</v>
+        <v>84</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>631</v>
+      </c>
+      <c r="F124" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>633</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="K124" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="M124" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="N124" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="O124" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="P124" s="10" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q124" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>1067</v>
       </c>
       <c r="T124" s="41"/>
       <c r="U124" s="41"/>
@@ -9551,34 +9537,49 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B125" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C125" s="45" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D125" s="45" t="s">
-        <v>639</v>
-      </c>
-      <c r="E125" s="45" t="s">
-        <v>640</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>641</v>
-      </c>
-      <c r="G125" s="11" t="s">
-        <v>963</v>
-      </c>
-      <c r="H125" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="I125" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="J125" s="8" t="s">
-        <v>923</v>
+        <v>85</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="I125" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="J125" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="K125" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="M125" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="N125" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>903</v>
       </c>
       <c r="T125" s="41"/>
       <c r="U125" s="41"/>
@@ -9587,46 +9588,34 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>642</v>
-      </c>
-      <c r="D126" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E126" s="13" t="s">
-        <v>643</v>
-      </c>
-      <c r="F126" s="13" t="s">
-        <v>644</v>
+        <v>86</v>
+      </c>
+      <c r="B126" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="C126" s="45" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D126" s="45" t="s">
+        <v>639</v>
+      </c>
+      <c r="E126" s="45" t="s">
+        <v>640</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>641</v>
       </c>
       <c r="G126" s="11" t="s">
-        <v>645</v>
-      </c>
-      <c r="H126" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="I126" s="13" t="s">
-        <v>605</v>
-      </c>
-      <c r="J126" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>647</v>
-      </c>
-      <c r="L126" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="M126" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="N126" s="8" t="s">
-        <v>999</v>
+        <v>963</v>
+      </c>
+      <c r="H126" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="I126" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="J126" s="8" t="s">
+        <v>923</v>
       </c>
       <c r="T126" s="41"/>
       <c r="U126" s="41"/>
@@ -9635,43 +9624,46 @@
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C127" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B127" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="D127" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="E127" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="F127" s="11" t="s">
-        <v>650</v>
-      </c>
-      <c r="G127" s="9" t="s">
-        <v>651</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>521</v>
-      </c>
-      <c r="I127" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="J127" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K127" s="8" t="s">
-        <v>926</v>
-      </c>
-      <c r="L127" s="8" t="s">
-        <v>1022</v>
-      </c>
-      <c r="M127" s="1" t="s">
-        <v>1068</v>
+      <c r="E127" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="F127" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I127" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="J127" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="K127" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="L127" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="M127" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="N127" s="8" t="s">
+        <v>999</v>
       </c>
       <c r="T127" s="41"/>
       <c r="U127" s="41"/>
@@ -9680,113 +9672,140 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C128" s="14" t="s">
-        <v>652</v>
+        <v>88</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>653</v>
-      </c>
-      <c r="E128" s="13" t="s">
-        <v>654</v>
-      </c>
-      <c r="F128" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="G128" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="H128" s="5" t="s">
-        <v>656</v>
+        <v>648</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="F128" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>521</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="J128" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="K128" s="11" t="s">
-        <v>657</v>
-      </c>
-      <c r="L128" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="M128" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="N128" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="O128" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q128" s="6" t="s">
-        <v>898</v>
-      </c>
-      <c r="R128" s="7" t="s">
-        <v>899</v>
-      </c>
-      <c r="S128" s="9" t="s">
-        <v>944</v>
-      </c>
-      <c r="T128" s="47" t="s">
-        <v>993</v>
-      </c>
-      <c r="U128" s="41" t="s">
-        <v>183</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="J128" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="L128" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="T128" s="41"/>
+      <c r="U128" s="41"/>
       <c r="V128" s="41"/>
       <c r="W128" s="2"/>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>661</v>
+        <v>89</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>654</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>417</v>
+        <v>655</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>662</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="T129" s="41"/>
-      <c r="U129" s="41"/>
+        <v>421</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="I129" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K129" s="11" t="s">
+        <v>657</v>
+      </c>
+      <c r="L129" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="M129" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="N129" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="O129" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="P129" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q129" s="6" t="s">
+        <v>898</v>
+      </c>
+      <c r="R129" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="S129" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="T129" s="47" t="s">
+        <v>993</v>
+      </c>
+      <c r="U129" s="41" t="s">
+        <v>183</v>
+      </c>
       <c r="V129" s="41"/>
       <c r="W129" s="2"/>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>947</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>478</v>
+        <v>146</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="F130" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="H130" s="13" t="s">
+        <v>312</v>
       </c>
       <c r="T130" s="41"/>
       <c r="U130" s="41"/>
@@ -9795,58 +9814,16 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>664</v>
-      </c>
-      <c r="F131" s="10" t="s">
-        <v>665</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="H131" s="11" t="s">
-        <v>666</v>
-      </c>
-      <c r="I131" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="K131" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="L131" s="13" t="s">
-        <v>808</v>
-      </c>
-      <c r="M131" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="N131" s="7" t="s">
-        <v>923</v>
-      </c>
-      <c r="O131" s="7" t="s">
-        <v>924</v>
-      </c>
-      <c r="P131" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q131" s="9" t="s">
-        <v>1032</v>
-      </c>
-      <c r="R131" s="1" t="s">
-        <v>1055</v>
+        <v>946</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>478</v>
       </c>
       <c r="T131" s="41"/>
       <c r="U131" s="41"/>
@@ -9855,61 +9832,58 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>667</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>668</v>
-      </c>
-      <c r="E132" s="13" t="s">
-        <v>669</v>
+        <v>90</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>664</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>670</v>
+        <v>665</v>
+      </c>
+      <c r="G132" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="I132" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="J132" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="K132" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="L132" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="M132" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="J132" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="K132" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="L132" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="M132" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="N132" s="7" t="s">
-        <v>862</v>
-      </c>
-      <c r="O132" s="11" t="s">
-        <v>819</v>
-      </c>
-      <c r="P132" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q132" s="6" t="s">
         <v>923</v>
       </c>
-      <c r="R132" s="8" t="s">
-        <v>906</v>
-      </c>
-      <c r="S132" s="8" t="s">
-        <v>1040</v>
+      <c r="O132" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="P132" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q132" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="R132" s="1" t="s">
+        <v>1055</v>
       </c>
       <c r="T132" s="41"/>
       <c r="U132" s="41"/>
@@ -9918,40 +9892,61 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B133" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B133" s="11" t="s">
         <v>157</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="H133" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="I133" s="10" t="s">
-        <v>895</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>996</v>
-      </c>
-      <c r="K133" s="8" t="s">
-        <v>997</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>1059</v>
+        <v>667</v>
+      </c>
+      <c r="D133" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="F133" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="K133" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="L133" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="M133" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N133" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="O133" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="P133" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q133" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="R133" s="8" t="s">
+        <v>906</v>
+      </c>
+      <c r="S133" s="8" t="s">
+        <v>1040</v>
       </c>
       <c r="T133" s="41"/>
       <c r="U133" s="41"/>
@@ -9960,37 +9955,40 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B134" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C134" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="E134" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F134" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="G134" s="13" t="s">
-        <v>833</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>888</v>
-      </c>
-      <c r="I134" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="I134" s="10" t="s">
         <v>895</v>
       </c>
-      <c r="J134" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="K134" s="9" t="s">
-        <v>981</v>
+      <c r="J134" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>1059</v>
       </c>
       <c r="T134" s="41"/>
       <c r="U134" s="41"/>
@@ -9999,49 +9997,37 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D135" s="10" t="s">
-        <v>353</v>
+        <v>92</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>225</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>675</v>
+        <v>183</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="G135" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>170</v>
+        <v>850</v>
+      </c>
+      <c r="G135" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>888</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="J135" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="K135" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="L135" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="M135" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="N135" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="O135" s="6" t="s">
-        <v>1018</v>
+        <v>895</v>
+      </c>
+      <c r="J135" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="K135" s="9" t="s">
+        <v>981</v>
       </c>
       <c r="T135" s="41"/>
       <c r="U135" s="41"/>
@@ -10050,31 +10036,49 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C136" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="D136" s="12" t="s">
-        <v>678</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>679</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>278</v>
+        <v>93</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>675</v>
+      </c>
+      <c r="F136" s="11" t="s">
+        <v>239</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="H136" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>1063</v>
+        <v>192</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="I136" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="K136" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="L136" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="M136" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="N136" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>1018</v>
       </c>
       <c r="T136" s="41"/>
       <c r="U136" s="41"/>
@@ -10083,28 +10087,31 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B137" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="C137" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="E137" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="F137" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="G137" s="9" t="s">
-        <v>919</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>1049</v>
+        <v>94</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>1063</v>
       </c>
       <c r="T137" s="41"/>
       <c r="U137" s="41"/>
@@ -10113,46 +10120,28 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B138" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C138" s="11" t="s">
-        <v>680</v>
-      </c>
-      <c r="D138" s="13" t="s">
-        <v>608</v>
-      </c>
-      <c r="E138" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="F138" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="G138" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H138" s="8" t="s">
-        <v>681</v>
-      </c>
-      <c r="I138" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="J138" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="K138" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="L138" s="6" t="s">
-        <v>868</v>
-      </c>
-      <c r="M138" s="11" t="s">
-        <v>944</v>
-      </c>
-      <c r="N138" s="8" t="s">
-        <v>1022</v>
+        <v>95</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="E138" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F138" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>1049</v>
       </c>
       <c r="T138" s="41"/>
       <c r="U138" s="41"/>
@@ -10161,31 +10150,46 @@
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="B139" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C139" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="D139" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="E139" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="F139" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>685</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="I139" s="10" t="s">
-        <v>1028</v>
+      <c r="C139" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>608</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="J139" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="K139" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="L139" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="M139" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="N139" s="8" t="s">
+        <v>1022</v>
       </c>
       <c r="T139" s="41"/>
       <c r="U139" s="41"/>
@@ -10194,55 +10198,31 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>97</v>
+        <v>148</v>
       </c>
       <c r="B140" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>688</v>
-      </c>
-      <c r="F140" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="G140" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="H140" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="I140" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="J140" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="K140" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="L140" s="6" t="s">
-        <v>689</v>
-      </c>
-      <c r="M140" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="N140" s="10" t="s">
-        <v>869</v>
-      </c>
-      <c r="O140" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="P140" s="12" t="s">
+      <c r="C140" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="F140" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="H140" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="Q140" s="6" t="s">
-        <v>1032</v>
+      <c r="I140" s="10" t="s">
+        <v>1028</v>
       </c>
       <c r="T140" s="41"/>
       <c r="U140" s="41"/>
@@ -10251,55 +10231,55 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B141" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B141" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>964</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F141" s="13" t="s">
-        <v>605</v>
+        <v>686</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>240</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="H141" s="8" t="s">
-        <v>232</v>
+        <v>357</v>
+      </c>
+      <c r="H141" s="13" t="s">
+        <v>471</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="J141" s="13" t="s">
-        <v>857</v>
+        <v>220</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>358</v>
       </c>
       <c r="K141" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="L141" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="L141" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="M141" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="M141" s="11" t="s">
-        <v>801</v>
-      </c>
-      <c r="N141" s="8" t="s">
-        <v>815</v>
-      </c>
-      <c r="O141" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="P141" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="Q141" s="10" t="s">
-        <v>985</v>
+      <c r="N141" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="O141" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="P141" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q141" s="6" t="s">
+        <v>1032</v>
       </c>
       <c r="T141" s="41"/>
       <c r="U141" s="41"/>
@@ -10308,58 +10288,55 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C142" s="13" t="s">
-        <v>691</v>
+        <v>98</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>690</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>692</v>
-      </c>
-      <c r="E142" s="11" t="s">
-        <v>693</v>
+        <v>964</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="F142" s="13" t="s">
-        <v>694</v>
+        <v>605</v>
       </c>
       <c r="G142" s="11" t="s">
-        <v>695</v>
-      </c>
-      <c r="H142" s="11" t="s">
-        <v>696</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>403</v>
+        <v>289</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="I142" s="13" t="s">
+        <v>272</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>326</v>
+        <v>857</v>
       </c>
       <c r="K142" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="L142" s="13" t="s">
-        <v>697</v>
-      </c>
-      <c r="M142" s="13" t="s">
-        <v>698</v>
+        <v>373</v>
+      </c>
+      <c r="L142" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="M142" s="11" t="s">
+        <v>801</v>
       </c>
       <c r="N142" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="O142" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="P142" s="10" t="s">
-        <v>173</v>
+        <v>815</v>
+      </c>
+      <c r="O142" s="8" t="s">
+        <v>900</v>
+      </c>
+      <c r="P142" s="9" t="s">
+        <v>895</v>
       </c>
       <c r="Q142" s="10" t="s">
-        <v>906</v>
-      </c>
-      <c r="R142" s="10" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="T142" s="41"/>
       <c r="U142" s="41"/>
@@ -10368,34 +10345,58 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B143" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B143" s="11" t="s">
         <v>157</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>699</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>700</v>
+        <v>691</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>692</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>438</v>
+        <v>693</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="I143" s="9" t="s">
-        <v>889</v>
+        <v>695</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>696</v>
+      </c>
+      <c r="I143" s="6" t="s">
+        <v>403</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>991</v>
+        <v>326</v>
+      </c>
+      <c r="K143" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="L143" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="M143" s="13" t="s">
+        <v>698</v>
+      </c>
+      <c r="N143" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="O143" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="P143" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q143" s="10" t="s">
+        <v>906</v>
+      </c>
+      <c r="R143" s="10" t="s">
+        <v>970</v>
       </c>
       <c r="T143" s="41"/>
       <c r="U143" s="41"/>
@@ -10404,49 +10405,34 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B144" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C144" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>595</v>
+      <c r="C144" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="D144" s="13" t="s">
+        <v>700</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>703</v>
+        <v>438</v>
       </c>
       <c r="F144" s="13" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>371</v>
-      </c>
-      <c r="H144" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="I144" s="11" t="s">
-        <v>284</v>
+        <v>521</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>889</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="K144" s="11" t="s">
-        <v>705</v>
-      </c>
-      <c r="L144" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="M144" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N144" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="O144" s="9" t="s">
-        <v>1038</v>
+        <v>991</v>
       </c>
       <c r="T144" s="41"/>
       <c r="U144" s="41"/>
@@ -10455,58 +10441,49 @@
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B145" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C145" s="13" t="s">
-        <v>421</v>
+        <v>101</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>702</v>
       </c>
       <c r="D145" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="E145" s="13" t="s">
-        <v>824</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H145" s="13" t="s">
-        <v>707</v>
-      </c>
-      <c r="I145" s="10" t="s">
-        <v>708</v>
+        <v>595</v>
+      </c>
+      <c r="E145" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="F145" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="G145" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I145" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="K145" s="13" t="s">
-        <v>709</v>
-      </c>
-      <c r="L145" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="K145" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="L145" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="M145" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="N145" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="O145" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="P145" s="8" t="s">
-        <v>804</v>
-      </c>
-      <c r="Q145" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="R145" s="6" t="s">
+      <c r="M145" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="N145" s="8" t="s">
         <v>162</v>
+      </c>
+      <c r="O145" s="9" t="s">
+        <v>1038</v>
       </c>
       <c r="T145" s="41"/>
       <c r="U145" s="41"/>
@@ -10515,52 +10492,58 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B146" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>710</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>711</v>
+        <v>102</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C146" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>706</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>712</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="H146" s="11" t="s">
-        <v>713</v>
-      </c>
-      <c r="I146" s="13" t="s">
-        <v>605</v>
-      </c>
-      <c r="J146" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="K146" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="L146" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="M146" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="N146" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G146" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="O146" s="10" t="s">
-        <v>955</v>
-      </c>
-      <c r="P146" s="13" t="s">
-        <v>273</v>
+      <c r="H146" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="I146" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="J146" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="K146" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="L146" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M146" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="N146" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="O146" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="P146" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="Q146" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="R146" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="T146" s="41"/>
       <c r="U146" s="41"/>
@@ -10569,28 +10552,52 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C147" s="13" t="s">
-        <v>716</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>717</v>
-      </c>
-      <c r="E147" s="10" t="s">
-        <v>718</v>
-      </c>
-      <c r="F147" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="G147" s="10" t="s">
-        <v>719</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>915</v>
+        <v>103</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C147" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>711</v>
+      </c>
+      <c r="E147" s="13" t="s">
+        <v>712</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="G147" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="I147" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="J147" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="K147" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="L147" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="M147" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="N147" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="O147" s="10" t="s">
+        <v>955</v>
+      </c>
+      <c r="P147" s="13" t="s">
+        <v>273</v>
       </c>
       <c r="T147" s="41"/>
       <c r="U147" s="41"/>
@@ -10599,31 +10606,28 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>795</v>
-      </c>
-      <c r="D148" s="10" t="s">
-        <v>573</v>
+        <v>104</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C148" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>717</v>
       </c>
       <c r="E148" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="F148" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="G148" s="13" t="s">
-        <v>720</v>
+        <v>718</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>719</v>
       </c>
       <c r="H148" s="10" t="s">
-        <v>889</v>
-      </c>
-      <c r="I148" s="12" t="s">
-        <v>1023</v>
+        <v>915</v>
       </c>
       <c r="T148" s="41"/>
       <c r="U148" s="41"/>
@@ -10632,55 +10636,31 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>721</v>
-      </c>
-      <c r="D149" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="E149" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="F149" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="G149" s="10" t="s">
-        <v>722</v>
+      <c r="C149" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G149" s="13" t="s">
+        <v>720</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="I149" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="J149" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="K149" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="L149" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="M149" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="N149" s="6" t="s">
-        <v>877</v>
-      </c>
-      <c r="O149" s="8" t="s">
-        <v>893</v>
-      </c>
-      <c r="P149" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q149" s="6" t="s">
-        <v>980</v>
+        <v>889</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>1023</v>
       </c>
       <c r="T149" s="41"/>
       <c r="U149" s="41"/>
@@ -10689,153 +10669,177 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C150" s="10" t="s">
-        <v>724</v>
-      </c>
-      <c r="D150" s="12" t="s">
-        <v>725</v>
-      </c>
-      <c r="E150" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F150" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F150" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="G150" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>258</v>
+      <c r="G150" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>289</v>
       </c>
       <c r="I150" s="8" t="s">
-        <v>726</v>
+        <v>195</v>
       </c>
       <c r="J150" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K150" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="L150" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="K150" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="L150" s="10" t="s">
-        <v>870</v>
-      </c>
-      <c r="M150" s="10" t="s">
+      <c r="M150" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="N150" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="O150" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="P150" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="N150" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="O150" s="8" t="s">
-        <v>800</v>
-      </c>
-      <c r="P150" s="12" t="s">
-        <v>832</v>
-      </c>
-      <c r="Q150" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="R150" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="S150" s="6" t="s">
-        <v>968</v>
-      </c>
-      <c r="T150" s="41" t="s">
-        <v>1066</v>
-      </c>
+      <c r="Q150" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="T150" s="41"/>
       <c r="U150" s="41"/>
       <c r="V150" s="41"/>
       <c r="W150" s="2"/>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>727</v>
+        <v>107</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>724</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>728</v>
-      </c>
-      <c r="E151" s="11" t="s">
-        <v>729</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>730</v>
-      </c>
-      <c r="G151" s="13" t="s">
-        <v>731</v>
-      </c>
-      <c r="H151" s="13" t="s">
-        <v>732</v>
-      </c>
-      <c r="I151" s="13" t="s">
-        <v>733</v>
-      </c>
-      <c r="J151" s="10" t="s">
-        <v>734</v>
+        <v>725</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G151" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I151" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="J151" s="11" t="s">
+        <v>183</v>
       </c>
       <c r="K151" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="L151" s="13" t="s">
-        <v>172</v>
+        <v>432</v>
+      </c>
+      <c r="L151" s="10" t="s">
+        <v>870</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>735</v>
+        <v>173</v>
       </c>
       <c r="N151" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="O151" s="12" t="s">
-        <v>880</v>
-      </c>
-      <c r="P151" s="13" t="s">
-        <v>939</v>
+        <v>373</v>
+      </c>
+      <c r="O151" s="8" t="s">
+        <v>800</v>
+      </c>
+      <c r="P151" s="12" t="s">
+        <v>832</v>
       </c>
       <c r="Q151" s="8" t="s">
-        <v>889</v>
-      </c>
-      <c r="T151" s="41"/>
+        <v>440</v>
+      </c>
+      <c r="R151" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="S151" s="6" t="s">
+        <v>968</v>
+      </c>
+      <c r="T151" s="41" t="s">
+        <v>1066</v>
+      </c>
       <c r="U151" s="41"/>
       <c r="V151" s="41"/>
       <c r="W151" s="2"/>
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C152" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="D152" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E152" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="H152" s="11" t="s">
-        <v>940</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>1071</v>
+        <v>108</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>727</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="E152" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>731</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="J152" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="K152" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="L152" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="M152" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="N152" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="O152" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="P152" s="13" t="s">
+        <v>939</v>
+      </c>
+      <c r="Q152" s="8" t="s">
+        <v>889</v>
       </c>
       <c r="T152" s="41"/>
       <c r="U152" s="41"/>
@@ -10844,22 +10848,31 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="B153" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C153" s="11" t="s">
-        <v>440</v>
-      </c>
-      <c r="D153" s="11" t="s">
-        <v>893</v>
-      </c>
-      <c r="E153" s="10" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>205</v>
+        <v>109</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E153" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="T153" s="41"/>
       <c r="U153" s="41"/>
@@ -10868,49 +10881,22 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B154" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C154" s="13" t="s">
-        <v>736</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="E154" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>737</v>
-      </c>
-      <c r="G154" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H154" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="I154" s="11" t="s">
-        <v>738</v>
-      </c>
-      <c r="J154" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="K154" s="9" t="s">
-        <v>1012</v>
-      </c>
-      <c r="L154" s="11" t="s">
-        <v>902</v>
-      </c>
-      <c r="M154" s="6" t="s">
-        <v>944</v>
-      </c>
-      <c r="N154" s="6" t="s">
-        <v>998</v>
-      </c>
-      <c r="O154" s="10" t="s">
-        <v>980</v>
+        <v>810</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D154" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="T154" s="41"/>
       <c r="U154" s="41"/>
@@ -10919,31 +10905,49 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D155" s="11" t="s">
-        <v>809</v>
+        <v>110</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C155" s="13" t="s">
+        <v>736</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>270</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>840</v>
-      </c>
-      <c r="F155" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="G155" s="13" t="s">
-        <v>920</v>
-      </c>
-      <c r="H155" s="8" t="s">
-        <v>988</v>
-      </c>
-      <c r="I155" s="8" t="s">
-        <v>1051</v>
+        <v>335</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>737</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="I155" s="11" t="s">
+        <v>738</v>
+      </c>
+      <c r="J155" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="K155" s="9" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L155" s="11" t="s">
+        <v>902</v>
+      </c>
+      <c r="M155" s="6" t="s">
+        <v>944</v>
+      </c>
+      <c r="N155" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="O155" s="10" t="s">
+        <v>980</v>
       </c>
       <c r="T155" s="41"/>
       <c r="U155" s="41"/>
@@ -10952,34 +10956,31 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B156" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B156" s="6" t="s">
         <v>157</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="D156" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="E156" s="10" t="s">
-        <v>741</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="G156" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>232</v>
+        <v>197</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>809</v>
+      </c>
+      <c r="E156" s="13" t="s">
+        <v>840</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G156" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>988</v>
       </c>
       <c r="I156" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="J156" s="8" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="T156" s="41"/>
       <c r="U156" s="41"/>
@@ -10988,52 +10989,34 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B157" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B157" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>451</v>
+        <v>739</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="E157" s="13" t="s">
-        <v>743</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>254</v>
+        <v>740</v>
+      </c>
+      <c r="E157" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>458</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>744</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>726</v>
-      </c>
-      <c r="I157" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="J157" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="K157" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L157" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="M157" s="11" t="s">
-        <v>819</v>
-      </c>
-      <c r="N157" s="10" t="s">
-        <v>903</v>
-      </c>
-      <c r="O157" s="10" t="s">
-        <v>1014</v>
-      </c>
-      <c r="P157" s="1" t="s">
         <v>339</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J157" s="8" t="s">
+        <v>1044</v>
       </c>
       <c r="T157" s="41"/>
       <c r="U157" s="41"/>
@@ -11042,40 +11025,52 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B158" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>577</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>746</v>
-      </c>
-      <c r="E158" s="10" t="s">
-        <v>747</v>
-      </c>
-      <c r="F158" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="G158" s="13" t="s">
-        <v>748</v>
-      </c>
-      <c r="H158" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="I158" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="J158" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="K158" s="6" t="s">
-        <v>915</v>
-      </c>
-      <c r="L158" s="13" t="s">
-        <v>1032</v>
+        <v>150</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>743</v>
+      </c>
+      <c r="F158" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="I158" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="J158" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="M158" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="N158" s="10" t="s">
+        <v>903</v>
+      </c>
+      <c r="O158" s="10" t="s">
+        <v>1014</v>
+      </c>
+      <c r="P158" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="T158" s="41"/>
       <c r="U158" s="41"/>
@@ -11084,58 +11079,40 @@
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>750</v>
-      </c>
-      <c r="D159" s="13" t="s">
-        <v>751</v>
-      </c>
-      <c r="E159" s="13" t="s">
-        <v>752</v>
+        <v>112</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>746</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>747</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>753</v>
-      </c>
-      <c r="G159" s="11" t="s">
-        <v>754</v>
+        <v>372</v>
+      </c>
+      <c r="G159" s="13" t="s">
+        <v>748</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>755</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>756</v>
-      </c>
-      <c r="J159" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="K159" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="L159" s="10" t="s">
-        <v>556</v>
-      </c>
-      <c r="M159" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="N159" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="O159" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="P159" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="Q159" s="6" t="s">
-        <v>1006</v>
-      </c>
-      <c r="R159" s="1" t="s">
-        <v>1057</v>
+        <v>749</v>
+      </c>
+      <c r="I159" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="J159" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="L159" s="13" t="s">
+        <v>1032</v>
       </c>
       <c r="T159" s="41"/>
       <c r="U159" s="41"/>
@@ -11144,37 +11121,58 @@
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B160" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C160" s="13" t="s">
-        <v>758</v>
-      </c>
-      <c r="D160" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>760</v>
+        <v>113</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="D160" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="E160" s="13" t="s">
+        <v>752</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>708</v>
-      </c>
-      <c r="G160" s="10" t="s">
-        <v>761</v>
+        <v>753</v>
+      </c>
+      <c r="G160" s="11" t="s">
+        <v>754</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>762</v>
-      </c>
-      <c r="I160" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="J160" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="K160" s="9" t="s">
-        <v>312</v>
+        <v>755</v>
+      </c>
+      <c r="I160" s="13" t="s">
+        <v>756</v>
+      </c>
+      <c r="J160" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="K160" s="13" t="s">
+        <v>757</v>
+      </c>
+      <c r="L160" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="M160" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="N160" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="O160" s="11" t="s">
+        <v>895</v>
+      </c>
+      <c r="P160" s="6" t="s">
+        <v>896</v>
+      </c>
+      <c r="Q160" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="R160" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="T160" s="41"/>
       <c r="U160" s="41"/>
@@ -11183,46 +11181,37 @@
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="D161" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="F161" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G161" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C161" s="13" t="s">
+        <v>758</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="E161" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="F161" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>761</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>762</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="J161" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="H161" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="I161" s="8" t="s">
-        <v>872</v>
-      </c>
-      <c r="J161" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="K161" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="L161" s="7" t="s">
-        <v>934</v>
-      </c>
-      <c r="M161" s="8" t="s">
-        <v>832</v>
-      </c>
-      <c r="N161" s="8" t="s">
-        <v>274</v>
+      <c r="K161" s="9" t="s">
+        <v>312</v>
       </c>
       <c r="T161" s="41"/>
       <c r="U161" s="41"/>
@@ -11231,37 +11220,46 @@
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B162" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C162" s="11" t="s">
-        <v>764</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>481</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>602</v>
-      </c>
-      <c r="F162" s="11" t="s">
-        <v>417</v>
+        <v>114</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="H162" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="J162" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="I162" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="J162" s="6" t="s">
-        <v>950</v>
-      </c>
-      <c r="K162" s="1" t="s">
-        <v>1056</v>
+      <c r="K162" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="L162" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="M162" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="N162" s="8" t="s">
+        <v>274</v>
       </c>
       <c r="T162" s="41"/>
       <c r="U162" s="41"/>
@@ -11270,43 +11268,37 @@
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C163" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="D163" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="E163" s="10" t="s">
-        <v>765</v>
-      </c>
-      <c r="F163" s="10" t="s">
-        <v>766</v>
-      </c>
-      <c r="G163" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="H163" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="I163" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="J163" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="K163" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="L163" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="M163" s="8" t="s">
-        <v>1039</v>
+        <v>115</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>764</v>
+      </c>
+      <c r="D163" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="E163" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="F163" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="H163" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="I163" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J163" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>1056</v>
       </c>
       <c r="T163" s="41"/>
       <c r="U163" s="41"/>
@@ -11315,147 +11307,153 @@
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C164" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F164" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G164" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H164" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="I164" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="J164" s="10" t="s">
-        <v>864</v>
-      </c>
-      <c r="K164" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="L164" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="M164" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="N164" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="O164" s="6" t="s">
-        <v>915</v>
-      </c>
-      <c r="P164" s="10" t="s">
-        <v>916</v>
-      </c>
-      <c r="Q164" s="8" t="s">
-        <v>945</v>
-      </c>
-      <c r="R164" s="11" t="s">
-        <v>833</v>
-      </c>
-      <c r="S164" s="8" t="s">
-        <v>992</v>
-      </c>
-      <c r="T164" s="44" t="s">
-        <v>1052</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C164" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="E164" s="10" t="s">
+        <v>765</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H164" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="J164" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="K164" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="L164" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="M164" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T164" s="41"/>
       <c r="U164" s="41"/>
       <c r="V164" s="41"/>
       <c r="W164" s="2"/>
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C165" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="G165" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J165" s="10" t="s">
+        <v>864</v>
+      </c>
+      <c r="K165" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D165" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="F165" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="G165" s="10" t="s">
+      <c r="L165" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="M165" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="N165" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="O165" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="H165" s="9" t="s">
-        <v>935</v>
-      </c>
-      <c r="I165" s="9" t="s">
-        <v>936</v>
-      </c>
-      <c r="J165" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="K165" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="L165" s="6" t="s">
-        <v>1019</v>
-      </c>
-      <c r="M165" s="6" t="s">
-        <v>980</v>
-      </c>
-      <c r="T165" s="41"/>
+      <c r="P165" s="10" t="s">
+        <v>916</v>
+      </c>
+      <c r="Q165" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="R165" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="S165" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="T165" s="44" t="s">
+        <v>1052</v>
+      </c>
       <c r="U165" s="41"/>
       <c r="V165" s="41"/>
       <c r="W165" s="2"/>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C166" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="E166" s="8" t="s">
-        <v>258</v>
+        <v>152</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>440</v>
       </c>
       <c r="F166" s="13" t="s">
-        <v>769</v>
-      </c>
-      <c r="G166" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="H166" s="12" t="s">
-        <v>808</v>
-      </c>
-      <c r="I166" s="10" t="s">
-        <v>173</v>
+        <v>875</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>936</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="K166" s="11" t="s">
         <v>232</v>
+      </c>
+      <c r="K166" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="L166" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="M166" s="6" t="s">
+        <v>980</v>
       </c>
       <c r="T166" s="41"/>
       <c r="U166" s="41"/>
@@ -11464,21 +11462,38 @@
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B167" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B167" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D167" s="45"/>
-      <c r="E167" s="45"/>
-      <c r="F167" s="45"/>
-      <c r="G167" s="45"/>
-      <c r="H167" s="45"/>
-      <c r="I167" s="45"/>
-      <c r="J167" s="45"/>
+        <v>768</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="E167" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="F167" s="13" t="s">
+        <v>769</v>
+      </c>
+      <c r="G167" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="I167" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="J167" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K167" s="11" t="s">
+        <v>232</v>
+      </c>
       <c r="T167" s="41"/>
       <c r="U167" s="41"/>
       <c r="V167" s="41"/>
@@ -11486,41 +11501,21 @@
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B168" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C168" s="11" t="s">
-        <v>770</v>
-      </c>
-      <c r="D168" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="F168" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="G168" s="13" t="s">
-        <v>840</v>
-      </c>
-      <c r="H168" s="13" t="s">
-        <v>912</v>
-      </c>
-      <c r="I168" s="11" t="s">
-        <v>971</v>
-      </c>
-      <c r="J168" s="10" t="s">
-        <v>972</v>
-      </c>
-      <c r="K168" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="L168" s="9" t="s">
-        <v>432</v>
-      </c>
+        <v>1031</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D168" s="45"/>
+      <c r="E168" s="45"/>
+      <c r="F168" s="45"/>
+      <c r="G168" s="45"/>
+      <c r="H168" s="45"/>
+      <c r="I168" s="45"/>
+      <c r="J168" s="45"/>
       <c r="T168" s="41"/>
       <c r="U168" s="41"/>
       <c r="V168" s="41"/>
@@ -11528,21 +11523,41 @@
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B169" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B169" s="9" t="s">
         <v>157</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>923</v>
-      </c>
-      <c r="D169" s="45"/>
-      <c r="E169" s="45"/>
-      <c r="F169" s="45"/>
-      <c r="G169" s="45"/>
-      <c r="H169" s="45"/>
-      <c r="I169" s="45"/>
-      <c r="J169" s="45"/>
+        <v>770</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G169" s="13" t="s">
+        <v>840</v>
+      </c>
+      <c r="H169" s="13" t="s">
+        <v>912</v>
+      </c>
+      <c r="I169" s="11" t="s">
+        <v>971</v>
+      </c>
+      <c r="J169" s="10" t="s">
+        <v>972</v>
+      </c>
+      <c r="K169" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="L169" s="9" t="s">
+        <v>432</v>
+      </c>
       <c r="T169" s="41"/>
       <c r="U169" s="41"/>
       <c r="V169" s="41"/>
@@ -11550,32 +11565,21 @@
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B170" s="10" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B170" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>772</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="E170" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="F170" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="G170" s="10" t="s">
-        <v>893</v>
-      </c>
-      <c r="H170" s="13" t="s">
-        <v>952</v>
-      </c>
-      <c r="I170" s="1" t="s">
-        <v>252</v>
-      </c>
+        <v>923</v>
+      </c>
+      <c r="D170" s="45"/>
+      <c r="E170" s="45"/>
+      <c r="F170" s="45"/>
+      <c r="G170" s="45"/>
+      <c r="H170" s="45"/>
+      <c r="I170" s="45"/>
+      <c r="J170" s="45"/>
       <c r="T170" s="41"/>
       <c r="U170" s="41"/>
       <c r="V170" s="41"/>
@@ -11583,52 +11587,31 @@
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="D171" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="D171" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E171" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="E171" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>965</v>
+      <c r="F171" s="10" t="s">
+        <v>481</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="I171" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="J171" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="K171" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="L171" s="10" t="s">
         <v>893</v>
       </c>
-      <c r="M171" s="8" t="s">
-        <v>923</v>
-      </c>
-      <c r="N171" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="O171" s="6" t="s">
-        <v>1020</v>
-      </c>
-      <c r="P171" s="10" t="s">
-        <v>869</v>
+      <c r="H171" s="13" t="s">
+        <v>952</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="T171" s="41"/>
       <c r="U171" s="41"/>
@@ -11637,28 +11620,52 @@
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C172" s="11" t="s">
-        <v>676</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>875</v>
+        <v>120</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="D172" s="10" t="s">
+        <v>192</v>
       </c>
       <c r="E172" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="I172" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="K172" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="L172" s="10" t="s">
+        <v>893</v>
+      </c>
+      <c r="M172" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="F172" s="6" t="s">
-        <v>889</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>987</v>
-      </c>
-      <c r="H172" s="9" t="s">
-        <v>439</v>
+      <c r="N172" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="O172" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="P172" s="10" t="s">
+        <v>869</v>
       </c>
       <c r="T172" s="41"/>
       <c r="U172" s="41"/>
@@ -11667,46 +11674,28 @@
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C173" s="13" t="s">
-        <v>644</v>
+        <v>822</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>676</v>
       </c>
       <c r="D173" s="13" t="s">
-        <v>775</v>
-      </c>
-      <c r="E173" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="F173" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="G173" s="8" t="s">
-        <v>776</v>
-      </c>
-      <c r="H173" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="I173" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="J173" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="K173" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="L173" s="11" t="s">
-        <v>828</v>
-      </c>
-      <c r="M173" s="12" t="s">
-        <v>931</v>
-      </c>
-      <c r="N173" s="13" t="s">
-        <v>432</v>
+        <v>875</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>439</v>
       </c>
       <c r="T173" s="41"/>
       <c r="U173" s="41"/>
@@ -11715,34 +11704,46 @@
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>157</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>777</v>
-      </c>
-      <c r="D174" s="12" t="s">
-        <v>778</v>
+        <v>644</v>
+      </c>
+      <c r="D174" s="13" t="s">
+        <v>775</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>780</v>
-      </c>
-      <c r="G174" s="6" t="s">
-        <v>161</v>
+        <v>273</v>
+      </c>
+      <c r="F174" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>776</v>
       </c>
       <c r="H174" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I174" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="J174" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="I174" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="J174" s="8" t="s">
-        <v>278</v>
+      <c r="K174" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="L174" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="M174" s="12" t="s">
+        <v>931</v>
+      </c>
+      <c r="N174" s="13" t="s">
+        <v>432</v>
       </c>
       <c r="T174" s="41"/>
       <c r="U174" s="41"/>
@@ -11751,37 +11752,34 @@
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C175" s="10" t="s">
-        <v>781</v>
-      </c>
-      <c r="D175" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="H175" s="10" t="s">
-        <v>840</v>
-      </c>
-      <c r="I175" s="10" t="s">
+      <c r="C175" s="13" t="s">
+        <v>777</v>
+      </c>
+      <c r="D175" s="12" t="s">
+        <v>778</v>
+      </c>
+      <c r="E175" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="F175" s="13" t="s">
+        <v>780</v>
+      </c>
+      <c r="G175" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="I175" s="9" t="s">
         <v>895</v>
       </c>
-      <c r="J175" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="K175" s="6" t="s">
-        <v>1042</v>
+      <c r="J175" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="T175" s="41"/>
       <c r="U175" s="41"/>
@@ -11789,57 +11787,96 @@
       <c r="W175" s="2"/>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="D176" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E176" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>873</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="I176" s="10" t="s">
+        <v>895</v>
+      </c>
+      <c r="J176" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="K176" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="T176" s="41"/>
+      <c r="U176" s="41"/>
+      <c r="V176" s="41"/>
+      <c r="W176" s="2"/>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B176" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="C176" s="17" t="s">
+      <c r="B177" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C177" s="17" t="s">
         <v>782</v>
       </c>
-      <c r="D176" s="18" t="s">
+      <c r="D177" s="18" t="s">
         <v>526</v>
       </c>
-      <c r="E176" s="20" t="s">
+      <c r="E177" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F176" s="19" t="s">
+      <c r="F177" s="19" t="s">
         <v>783</v>
       </c>
-      <c r="G176" s="16" t="s">
+      <c r="G177" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="H176" s="18" t="s">
+      <c r="H177" s="18" t="s">
         <v>855</v>
       </c>
-      <c r="I176" s="36" t="s">
+      <c r="I177" s="36" t="s">
         <v>674</v>
       </c>
-      <c r="J176" s="18" t="s">
+      <c r="J177" s="18" t="s">
         <v>804</v>
       </c>
-      <c r="K176" s="18" t="s">
+      <c r="K177" s="18" t="s">
         <v>898</v>
       </c>
-      <c r="L176" s="16" t="s">
+      <c r="L177" s="16" t="s">
         <v>930</v>
       </c>
-      <c r="M176" s="52" t="s">
+      <c r="M177" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="N176" s="52" t="s">
+      <c r="N177" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="O176" s="3"/>
-      <c r="P176" s="3"/>
-      <c r="Q176" s="3"/>
-      <c r="R176" s="3"/>
-      <c r="S176" s="3"/>
-      <c r="T176" s="3"/>
-      <c r="U176" s="3"/>
-      <c r="V176" s="3"/>
-      <c r="W176" s="4"/>
+      <c r="O177" s="3"/>
+      <c r="P177" s="3"/>
+      <c r="Q177" s="3"/>
+      <c r="R177" s="3"/>
+      <c r="S177" s="3"/>
+      <c r="T177" s="3"/>
+      <c r="U177" s="3"/>
+      <c r="V177" s="3"/>
+      <c r="W177" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="1080">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3255,6 +3255,15 @@
   </si>
   <si>
     <t>Locke</t>
+  </si>
+  <si>
+    <t>MVP T1</t>
+  </si>
+  <si>
+    <t>Prestige Magma Chamber</t>
+  </si>
+  <si>
+    <t>Heartsong</t>
   </si>
 </sst>
 </file>
@@ -3368,7 +3377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -3452,17 +3461,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -3480,9 +3478,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3598,9 +3596,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3631,16 +3626,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3978,7 +3964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W177"/>
+  <dimension ref="A1:X177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -3990,14 +3976,14 @@
     <col min="20" max="20" width="30.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="29.140625" style="1" customWidth="1"/>
     <col min="22" max="22" width="30.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="25.7109375" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="11.42578125" style="1"/>
+    <col min="23" max="24" width="25.7109375" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="35"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>799</v>
       </c>
@@ -4038,39 +4024,41 @@
         <v>792</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="S3" s="3"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X3" s="3"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="38"/>
       <c r="S4" s="3"/>
       <c r="T4" s="37"/>
       <c r="U4" s="37"/>
       <c r="V4" s="37"/>
-      <c r="W4" s="39"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W4" s="37"/>
+      <c r="X4" s="22"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -4114,9 +4102,10 @@
       <c r="T5" s="37"/>
       <c r="U5" s="37"/>
       <c r="V5" s="37"/>
-      <c r="W5" s="39"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W5" s="37"/>
+      <c r="X5" s="2"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -4174,18 +4163,19 @@
       <c r="S6" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="T6" s="48" t="s">
+      <c r="T6" s="47" t="s">
         <v>969</v>
       </c>
-      <c r="U6" s="44" t="s">
+      <c r="U6" s="43" t="s">
         <v>1032</v>
       </c>
-      <c r="V6" s="47" t="s">
+      <c r="V6" s="46" t="s">
         <v>1033</v>
       </c>
-      <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W6" s="40"/>
+      <c r="X6" s="2"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -4243,18 +4233,19 @@
       <c r="S7" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="T7" s="42" t="s">
+      <c r="T7" s="41" t="s">
         <v>855</v>
       </c>
-      <c r="U7" s="47" t="s">
+      <c r="U7" s="46" t="s">
         <v>893</v>
       </c>
-      <c r="V7" s="42" t="s">
+      <c r="V7" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W7" s="40"/>
+      <c r="X7" s="2"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>802</v>
       </c>
@@ -4273,12 +4264,13 @@
       <c r="F8" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="2"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -4330,11 +4322,12 @@
       <c r="Q9" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="T9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="2"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>995</v>
       </c>
@@ -4344,25 +4337,28 @@
       <c r="C10" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D10" s="44" t="s">
+        <v>980</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="2"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -4411,12 +4407,13 @@
       <c r="P11" s="10" t="s">
         <v>1018</v>
       </c>
-      <c r="T11" s="41"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="2"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -4459,12 +4456,13 @@
       <c r="N12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="2"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -4522,14 +4520,15 @@
       <c r="S13" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="T13" s="41" t="s">
+      <c r="T13" s="40" t="s">
         <v>1065</v>
       </c>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="2"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -4554,12 +4553,13 @@
       <c r="H14" s="6" t="s">
         <v>1034</v>
       </c>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
@@ -4617,18 +4617,19 @@
       <c r="S15" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="T15" s="47" t="s">
+      <c r="T15" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="U15" s="42" t="s">
+      <c r="U15" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="V15" s="49" t="s">
+      <c r="V15" s="48" t="s">
         <v>432</v>
       </c>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W15" s="40"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>9</v>
       </c>
@@ -4653,12 +4654,13 @@
       <c r="H16" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T16" s="40"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="40"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>973</v>
       </c>
@@ -4671,16 +4673,17 @@
       <c r="D17" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="44" t="s">
         <v>903</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="F17" s="44"/>
+      <c r="T17" s="40"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -4708,12 +4711,13 @@
       <c r="I18" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T18" s="40"/>
+      <c r="U18" s="40"/>
+      <c r="V18" s="40"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -4744,12 +4748,13 @@
       <c r="J19" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T19" s="40"/>
+      <c r="U19" s="40"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>874</v>
       </c>
@@ -4765,12 +4770,16 @@
       <c r="E20" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="T20" s="40"/>
+      <c r="U20" s="40"/>
+      <c r="V20" s="40"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="2"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -4825,12 +4834,13 @@
       <c r="R21" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T21" s="40"/>
+      <c r="U21" s="40"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="2"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>124</v>
       </c>
@@ -4876,12 +4886,13 @@
       <c r="O22" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="2"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
@@ -4912,12 +4923,13 @@
       <c r="J23" s="10" t="s">
         <v>1024</v>
       </c>
-      <c r="T23" s="41"/>
-      <c r="U23" s="41"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="40"/>
+      <c r="W23" s="40"/>
+      <c r="X23" s="2"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>929</v>
       </c>
@@ -4933,12 +4945,13 @@
       <c r="E24" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="T24" s="41"/>
-      <c r="U24" s="41"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T24" s="40"/>
+      <c r="U24" s="40"/>
+      <c r="V24" s="40"/>
+      <c r="W24" s="40"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
@@ -4996,16 +5009,17 @@
       <c r="S25" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="T25" s="47" t="s">
+      <c r="T25" s="46" t="s">
         <v>1001</v>
       </c>
-      <c r="U25" s="44" t="s">
+      <c r="U25" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="V25" s="41"/>
-      <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V25" s="40"/>
+      <c r="W25" s="40"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>125</v>
       </c>
@@ -5036,12 +5050,13 @@
       <c r="J26" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="T26" s="41"/>
-      <c r="U26" s="41"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T26" s="40"/>
+      <c r="U26" s="40"/>
+      <c r="V26" s="40"/>
+      <c r="W26" s="40"/>
+      <c r="X26" s="2"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
@@ -5075,12 +5090,13 @@
       <c r="K27" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="T27" s="41"/>
-      <c r="U27" s="41"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T27" s="40"/>
+      <c r="U27" s="40"/>
+      <c r="V27" s="40"/>
+      <c r="W27" s="40"/>
+      <c r="X27" s="2"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -5120,12 +5136,13 @@
       <c r="M28" s="9" t="s">
         <v>1048</v>
       </c>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T28" s="40"/>
+      <c r="U28" s="40"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="40"/>
+      <c r="X28" s="2"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>17</v>
       </c>
@@ -5165,12 +5182,13 @@
       <c r="M29" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="T29" s="41"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="41"/>
-      <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T29" s="40"/>
+      <c r="U29" s="40"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="40"/>
+      <c r="X29" s="2"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>18</v>
       </c>
@@ -5222,12 +5240,13 @@
       <c r="Q30" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="T30" s="41"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T30" s="40"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="40"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="2"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>19</v>
       </c>
@@ -5282,12 +5301,13 @@
       <c r="R31" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="T31" s="41"/>
-      <c r="U31" s="41"/>
-      <c r="V31" s="41"/>
-      <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T31" s="40"/>
+      <c r="U31" s="40"/>
+      <c r="V31" s="40"/>
+      <c r="W31" s="40"/>
+      <c r="X31" s="2"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>126</v>
       </c>
@@ -5336,12 +5356,13 @@
       <c r="P32" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="41"/>
-      <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T32" s="40"/>
+      <c r="U32" s="40"/>
+      <c r="V32" s="40"/>
+      <c r="W32" s="40"/>
+      <c r="X32" s="2"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -5381,12 +5402,13 @@
       <c r="M33" s="13" t="s">
         <v>930</v>
       </c>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T33" s="40"/>
+      <c r="U33" s="40"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="2"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>127</v>
       </c>
@@ -5429,12 +5451,13 @@
       <c r="N34" s="9" t="s">
         <v>1007</v>
       </c>
-      <c r="T34" s="41"/>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T34" s="40"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="2"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>128</v>
       </c>
@@ -5468,12 +5491,13 @@
       <c r="K35" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="T35" s="41"/>
-      <c r="U35" s="41"/>
-      <c r="V35" s="41"/>
-      <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T35" s="40"/>
+      <c r="U35" s="40"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="2"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>21</v>
       </c>
@@ -5522,12 +5546,13 @@
       <c r="P36" s="6" t="s">
         <v>868</v>
       </c>
-      <c r="T36" s="41"/>
-      <c r="U36" s="41"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T36" s="40"/>
+      <c r="U36" s="40"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="2"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
@@ -5582,23 +5607,24 @@
       <c r="R37" s="6" t="s">
         <v>820</v>
       </c>
-      <c r="S37" s="40" t="s">
+      <c r="S37" s="39" t="s">
         <v>906</v>
       </c>
-      <c r="T37" s="43" t="s">
+      <c r="T37" s="42" t="s">
         <v>935</v>
       </c>
-      <c r="U37" s="44" t="s">
+      <c r="U37" s="43" t="s">
         <v>947</v>
       </c>
-      <c r="V37" s="49" t="s">
+      <c r="V37" s="48" t="s">
         <v>949</v>
       </c>
-      <c r="W37" s="50" t="s">
+      <c r="W37" s="46" t="s">
         <v>1014</v>
       </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X37" s="2"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>23</v>
       </c>
@@ -5641,12 +5667,13 @@
       <c r="N38" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-      <c r="V38" s="41"/>
-      <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T38" s="40"/>
+      <c r="U38" s="40"/>
+      <c r="V38" s="40"/>
+      <c r="W38" s="40"/>
+      <c r="X38" s="2"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>24</v>
       </c>
@@ -5701,12 +5728,13 @@
       <c r="R39" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T39" s="40"/>
+      <c r="U39" s="40"/>
+      <c r="V39" s="40"/>
+      <c r="W39" s="40"/>
+      <c r="X39" s="2"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>25</v>
       </c>
@@ -5749,12 +5777,13 @@
       <c r="N40" s="9" t="s">
         <v>970</v>
       </c>
-      <c r="T40" s="41"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="41"/>
-      <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T40" s="40"/>
+      <c r="U40" s="40"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="40"/>
+      <c r="X40" s="2"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>129</v>
       </c>
@@ -5791,12 +5820,16 @@
       <c r="L41" s="6" t="s">
         <v>1050</v>
       </c>
-      <c r="T41" s="41"/>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="M41" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="T41" s="40"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="2"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
@@ -5839,12 +5872,13 @@
       <c r="N42" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="T42" s="41"/>
-      <c r="U42" s="41"/>
-      <c r="V42" s="41"/>
-      <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T42" s="40"/>
+      <c r="U42" s="40"/>
+      <c r="V42" s="40"/>
+      <c r="W42" s="40"/>
+      <c r="X42" s="2"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -5899,12 +5933,13 @@
       <c r="R43" s="9" t="s">
         <v>1038</v>
       </c>
-      <c r="T43" s="41"/>
-      <c r="U43" s="41"/>
-      <c r="V43" s="41"/>
-      <c r="W43" s="2"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T43" s="40"/>
+      <c r="U43" s="40"/>
+      <c r="V43" s="40"/>
+      <c r="W43" s="40"/>
+      <c r="X43" s="2"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>28</v>
       </c>
@@ -5941,12 +5976,13 @@
       <c r="L44" s="12" t="s">
         <v>980</v>
       </c>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="2"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T44" s="40"/>
+      <c r="U44" s="40"/>
+      <c r="V44" s="40"/>
+      <c r="W44" s="40"/>
+      <c r="X44" s="2"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
@@ -5995,12 +6031,13 @@
       <c r="P45" s="13" t="s">
         <v>989</v>
       </c>
-      <c r="T45" s="41"/>
-      <c r="U45" s="41"/>
-      <c r="V45" s="41"/>
-      <c r="W45" s="2"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T45" s="40"/>
+      <c r="U45" s="40"/>
+      <c r="V45" s="40"/>
+      <c r="W45" s="40"/>
+      <c r="X45" s="2"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
@@ -6046,12 +6083,13 @@
       <c r="O46" s="10" t="s">
         <v>821</v>
       </c>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="2"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T46" s="40"/>
+      <c r="U46" s="40"/>
+      <c r="V46" s="40"/>
+      <c r="W46" s="40"/>
+      <c r="X46" s="2"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
@@ -6073,12 +6111,16 @@
       <c r="G47" s="13" t="s">
         <v>970</v>
       </c>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="2"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="H47" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="T47" s="40"/>
+      <c r="U47" s="40"/>
+      <c r="V47" s="40"/>
+      <c r="W47" s="40"/>
+      <c r="X47" s="2"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>32</v>
       </c>
@@ -6121,12 +6163,13 @@
       <c r="N48" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="T48" s="41"/>
-      <c r="U48" s="41"/>
-      <c r="V48" s="41"/>
-      <c r="W48" s="2"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T48" s="40"/>
+      <c r="U48" s="40"/>
+      <c r="V48" s="40"/>
+      <c r="W48" s="40"/>
+      <c r="X48" s="2"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>33</v>
       </c>
@@ -6160,12 +6203,13 @@
       <c r="K49" s="8" t="s">
         <v>1004</v>
       </c>
-      <c r="T49" s="41"/>
-      <c r="U49" s="41"/>
-      <c r="V49" s="41"/>
-      <c r="W49" s="2"/>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T49" s="40"/>
+      <c r="U49" s="40"/>
+      <c r="V49" s="40"/>
+      <c r="W49" s="40"/>
+      <c r="X49" s="2"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>941</v>
       </c>
@@ -6181,12 +6225,13 @@
       <c r="E50" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="T50" s="41"/>
-      <c r="U50" s="41"/>
-      <c r="V50" s="41"/>
-      <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T50" s="40"/>
+      <c r="U50" s="40"/>
+      <c r="V50" s="40"/>
+      <c r="W50" s="40"/>
+      <c r="X50" s="2"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>34</v>
       </c>
@@ -6211,12 +6256,13 @@
       <c r="H51" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="T51" s="41"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="41"/>
-      <c r="W51" s="2"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T51" s="40"/>
+      <c r="U51" s="40"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="40"/>
+      <c r="X51" s="2"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>35</v>
       </c>
@@ -6268,12 +6314,13 @@
       <c r="Q52" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="T52" s="41"/>
-      <c r="U52" s="41"/>
-      <c r="V52" s="41"/>
-      <c r="W52" s="2"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T52" s="40"/>
+      <c r="U52" s="40"/>
+      <c r="V52" s="40"/>
+      <c r="W52" s="40"/>
+      <c r="X52" s="2"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>130</v>
       </c>
@@ -6298,12 +6345,13 @@
       <c r="H53" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="T53" s="41"/>
-      <c r="U53" s="41"/>
-      <c r="V53" s="41"/>
-      <c r="W53" s="2"/>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T53" s="40"/>
+      <c r="U53" s="40"/>
+      <c r="V53" s="40"/>
+      <c r="W53" s="40"/>
+      <c r="X53" s="2"/>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>36</v>
       </c>
@@ -6355,12 +6403,13 @@
       <c r="Q54" s="6" t="s">
         <v>947</v>
       </c>
-      <c r="T54" s="41"/>
-      <c r="U54" s="41"/>
-      <c r="V54" s="41"/>
-      <c r="W54" s="2"/>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T54" s="40"/>
+      <c r="U54" s="40"/>
+      <c r="V54" s="40"/>
+      <c r="W54" s="40"/>
+      <c r="X54" s="2"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>131</v>
       </c>
@@ -6412,12 +6461,13 @@
       <c r="Q55" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="T55" s="41"/>
-      <c r="U55" s="41"/>
-      <c r="V55" s="41"/>
-      <c r="W55" s="2"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T55" s="40"/>
+      <c r="U55" s="40"/>
+      <c r="V55" s="40"/>
+      <c r="W55" s="40"/>
+      <c r="X55" s="2"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>37</v>
       </c>
@@ -6472,12 +6522,16 @@
       <c r="R56" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="T56" s="41"/>
-      <c r="U56" s="41"/>
-      <c r="V56" s="41"/>
-      <c r="W56" s="2"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S56" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="T56" s="40"/>
+      <c r="U56" s="40"/>
+      <c r="V56" s="40"/>
+      <c r="W56" s="40"/>
+      <c r="X56" s="2"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>38</v>
       </c>
@@ -6520,12 +6574,13 @@
       <c r="N57" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="T57" s="41"/>
-      <c r="U57" s="41"/>
-      <c r="V57" s="41"/>
-      <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T57" s="40"/>
+      <c r="U57" s="40"/>
+      <c r="V57" s="40"/>
+      <c r="W57" s="40"/>
+      <c r="X57" s="2"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>39</v>
       </c>
@@ -6571,12 +6626,13 @@
       <c r="O58" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="T58" s="41"/>
-      <c r="U58" s="41"/>
-      <c r="V58" s="41"/>
-      <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T58" s="40"/>
+      <c r="U58" s="40"/>
+      <c r="V58" s="40"/>
+      <c r="W58" s="40"/>
+      <c r="X58" s="2"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>40</v>
       </c>
@@ -6625,12 +6681,16 @@
       <c r="P59" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="T59" s="41"/>
-      <c r="U59" s="41"/>
-      <c r="V59" s="41"/>
-      <c r="W59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Q59" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="T59" s="40"/>
+      <c r="U59" s="40"/>
+      <c r="V59" s="40"/>
+      <c r="W59" s="40"/>
+      <c r="X59" s="2"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>132</v>
       </c>
@@ -6679,12 +6739,13 @@
       <c r="P60" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="T60" s="41"/>
-      <c r="U60" s="41"/>
-      <c r="V60" s="41"/>
-      <c r="W60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T60" s="40"/>
+      <c r="U60" s="40"/>
+      <c r="V60" s="40"/>
+      <c r="W60" s="40"/>
+      <c r="X60" s="2"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>42</v>
       </c>
@@ -6709,12 +6770,13 @@
       <c r="H61" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="T61" s="41"/>
-      <c r="U61" s="41"/>
-      <c r="V61" s="41"/>
-      <c r="W61" s="2"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T61" s="40"/>
+      <c r="U61" s="40"/>
+      <c r="V61" s="40"/>
+      <c r="W61" s="40"/>
+      <c r="X61" s="2"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>133</v>
       </c>
@@ -6766,12 +6828,13 @@
       <c r="Q62" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="T62" s="41"/>
-      <c r="U62" s="41"/>
-      <c r="V62" s="41"/>
-      <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T62" s="40"/>
+      <c r="U62" s="40"/>
+      <c r="V62" s="40"/>
+      <c r="W62" s="40"/>
+      <c r="X62" s="2"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>41</v>
       </c>
@@ -6808,12 +6871,13 @@
       <c r="L63" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="T63" s="41"/>
-      <c r="U63" s="41"/>
-      <c r="V63" s="41"/>
-      <c r="W63" s="2"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T63" s="40"/>
+      <c r="U63" s="40"/>
+      <c r="V63" s="40"/>
+      <c r="W63" s="40"/>
+      <c r="X63" s="2"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>134</v>
       </c>
@@ -6847,12 +6911,13 @@
       <c r="K64" s="10" t="s">
         <v>942</v>
       </c>
-      <c r="T64" s="41"/>
-      <c r="U64" s="41"/>
-      <c r="V64" s="41"/>
-      <c r="W64" s="2"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T64" s="40"/>
+      <c r="U64" s="40"/>
+      <c r="V64" s="40"/>
+      <c r="W64" s="40"/>
+      <c r="X64" s="2"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>43</v>
       </c>
@@ -6910,16 +6975,17 @@
       <c r="S65" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="T65" s="48" t="s">
+      <c r="T65" s="47" t="s">
         <v>1015</v>
       </c>
-      <c r="U65" s="48" t="s">
+      <c r="U65" s="47" t="s">
         <v>1052</v>
       </c>
-      <c r="V65" s="41"/>
-      <c r="W65" s="2"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V65" s="40"/>
+      <c r="W65" s="40"/>
+      <c r="X65" s="2"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>44</v>
       </c>
@@ -6977,12 +7043,13 @@
       <c r="S66" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="T66" s="41"/>
-      <c r="U66" s="41"/>
-      <c r="V66" s="41"/>
-      <c r="W66" s="2"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T66" s="40"/>
+      <c r="U66" s="40"/>
+      <c r="V66" s="40"/>
+      <c r="W66" s="40"/>
+      <c r="X66" s="2"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>45</v>
       </c>
@@ -7010,12 +7077,13 @@
       <c r="I67" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="T67" s="41"/>
-      <c r="U67" s="41"/>
-      <c r="V67" s="41"/>
-      <c r="W67" s="2"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T67" s="40"/>
+      <c r="U67" s="40"/>
+      <c r="V67" s="40"/>
+      <c r="W67" s="40"/>
+      <c r="X67" s="2"/>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>135</v>
       </c>
@@ -7052,12 +7120,13 @@
       <c r="L68" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="T68" s="41"/>
-      <c r="U68" s="41"/>
-      <c r="V68" s="41"/>
-      <c r="W68" s="2"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T68" s="40"/>
+      <c r="U68" s="40"/>
+      <c r="V68" s="40"/>
+      <c r="W68" s="40"/>
+      <c r="X68" s="2"/>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>46</v>
       </c>
@@ -7088,12 +7157,13 @@
       <c r="J69" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="T69" s="41"/>
-      <c r="U69" s="41"/>
-      <c r="V69" s="41"/>
-      <c r="W69" s="2"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T69" s="40"/>
+      <c r="U69" s="40"/>
+      <c r="V69" s="40"/>
+      <c r="W69" s="40"/>
+      <c r="X69" s="2"/>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>47</v>
       </c>
@@ -7127,12 +7197,13 @@
       <c r="K70" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="T70" s="41"/>
-      <c r="U70" s="41"/>
-      <c r="V70" s="41"/>
-      <c r="W70" s="2"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T70" s="40"/>
+      <c r="U70" s="40"/>
+      <c r="V70" s="40"/>
+      <c r="W70" s="40"/>
+      <c r="X70" s="2"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>136</v>
       </c>
@@ -7151,12 +7222,13 @@
       <c r="F71" s="12" t="s">
         <v>913</v>
       </c>
-      <c r="T71" s="41"/>
-      <c r="U71" s="41"/>
-      <c r="V71" s="41"/>
-      <c r="W71" s="2"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T71" s="40"/>
+      <c r="U71" s="40"/>
+      <c r="V71" s="40"/>
+      <c r="W71" s="40"/>
+      <c r="X71" s="2"/>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>48</v>
       </c>
@@ -7208,13 +7280,14 @@
       <c r="Q72" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R72" s="46"/>
-      <c r="T72" s="41"/>
-      <c r="U72" s="41"/>
-      <c r="V72" s="41"/>
-      <c r="W72" s="2"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R72" s="45"/>
+      <c r="T72" s="40"/>
+      <c r="U72" s="40"/>
+      <c r="V72" s="40"/>
+      <c r="W72" s="40"/>
+      <c r="X72" s="2"/>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>892</v>
       </c>
@@ -7230,12 +7303,13 @@
       <c r="E73" s="11" t="s">
         <v>935</v>
       </c>
-      <c r="T73" s="41"/>
-      <c r="U73" s="41"/>
-      <c r="V73" s="41"/>
-      <c r="W73" s="2"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T73" s="40"/>
+      <c r="U73" s="40"/>
+      <c r="V73" s="40"/>
+      <c r="W73" s="40"/>
+      <c r="X73" s="2"/>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>49</v>
       </c>
@@ -7284,12 +7358,13 @@
       <c r="P74" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="T74" s="41"/>
-      <c r="U74" s="41"/>
-      <c r="V74" s="41"/>
-      <c r="W74" s="2"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T74" s="40"/>
+      <c r="U74" s="40"/>
+      <c r="V74" s="40"/>
+      <c r="W74" s="40"/>
+      <c r="X74" s="2"/>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>50</v>
       </c>
@@ -7347,14 +7422,15 @@
       <c r="S75" s="10" t="s">
         <v>980</v>
       </c>
-      <c r="T75" s="43" t="s">
+      <c r="T75" s="42" t="s">
         <v>915</v>
       </c>
-      <c r="U75" s="41"/>
-      <c r="V75" s="41"/>
-      <c r="W75" s="2"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U75" s="40"/>
+      <c r="V75" s="40"/>
+      <c r="W75" s="40"/>
+      <c r="X75" s="2"/>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>51</v>
       </c>
@@ -7412,14 +7488,15 @@
       <c r="S76" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="T76" s="41" t="s">
+      <c r="T76" s="40" t="s">
         <v>1072</v>
       </c>
-      <c r="U76" s="41"/>
-      <c r="V76" s="41"/>
-      <c r="W76" s="2"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U76" s="40"/>
+      <c r="V76" s="40"/>
+      <c r="W76" s="40"/>
+      <c r="X76" s="2"/>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>52</v>
       </c>
@@ -7444,12 +7521,13 @@
       <c r="H77" s="8" t="s">
         <v>1052</v>
       </c>
-      <c r="T77" s="41"/>
-      <c r="U77" s="41"/>
-      <c r="V77" s="41"/>
-      <c r="W77" s="2"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T77" s="40"/>
+      <c r="U77" s="40"/>
+      <c r="V77" s="40"/>
+      <c r="W77" s="40"/>
+      <c r="X77" s="2"/>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>53</v>
       </c>
@@ -7483,35 +7561,37 @@
       <c r="K78" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="T78" s="41"/>
-      <c r="U78" s="41"/>
-      <c r="V78" s="41"/>
-      <c r="W78" s="2"/>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T78" s="40"/>
+      <c r="U78" s="40"/>
+      <c r="V78" s="40"/>
+      <c r="W78" s="40"/>
+      <c r="X78" s="2"/>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="B79" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" s="45" t="s">
+      <c r="B79" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
-      <c r="F79" s="45"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45"/>
-      <c r="J79" s="45"/>
-      <c r="K79" s="45"/>
-      <c r="T79" s="41"/>
-      <c r="U79" s="41"/>
-      <c r="V79" s="41"/>
-      <c r="W79" s="2"/>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+      <c r="T79" s="40"/>
+      <c r="U79" s="40"/>
+      <c r="V79" s="40"/>
+      <c r="W79" s="40"/>
+      <c r="X79" s="2"/>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>54</v>
       </c>
@@ -7560,12 +7640,13 @@
       <c r="P80" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="T80" s="41"/>
-      <c r="U80" s="41"/>
-      <c r="V80" s="41"/>
-      <c r="W80" s="2"/>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T80" s="40"/>
+      <c r="U80" s="40"/>
+      <c r="V80" s="40"/>
+      <c r="W80" s="40"/>
+      <c r="X80" s="2"/>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>55</v>
       </c>
@@ -7611,12 +7692,16 @@
       <c r="O81" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="T81" s="41"/>
-      <c r="U81" s="41"/>
-      <c r="V81" s="41"/>
-      <c r="W81" s="2"/>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="P81" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="T81" s="40"/>
+      <c r="U81" s="40"/>
+      <c r="V81" s="40"/>
+      <c r="W81" s="40"/>
+      <c r="X81" s="2"/>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>56</v>
       </c>
@@ -7677,17 +7762,18 @@
       <c r="T82" s="7" t="s">
         <v>920</v>
       </c>
-      <c r="U82" s="47" t="s">
+      <c r="U82" s="46" t="s">
         <v>906</v>
       </c>
-      <c r="V82" s="48" t="s">
+      <c r="V82" s="47" t="s">
         <v>869</v>
       </c>
-      <c r="W82" s="53" t="s">
+      <c r="W82" s="47" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X82" s="2"/>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>57</v>
       </c>
@@ -7736,12 +7822,13 @@
       <c r="P83" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="T83" s="41"/>
-      <c r="U83" s="41"/>
-      <c r="V83" s="41"/>
-      <c r="W83" s="2"/>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T83" s="40"/>
+      <c r="U83" s="40"/>
+      <c r="V83" s="40"/>
+      <c r="W83" s="40"/>
+      <c r="X83" s="2"/>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>137</v>
       </c>
@@ -7787,12 +7874,13 @@
       <c r="O84" s="9" t="s">
         <v>1028</v>
       </c>
-      <c r="T84" s="41"/>
-      <c r="U84" s="41"/>
-      <c r="V84" s="41"/>
-      <c r="W84" s="2"/>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T84" s="40"/>
+      <c r="U84" s="40"/>
+      <c r="V84" s="40"/>
+      <c r="W84" s="40"/>
+      <c r="X84" s="2"/>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>58</v>
       </c>
@@ -7832,12 +7920,13 @@
       <c r="M85" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="T85" s="41"/>
-      <c r="U85" s="41"/>
-      <c r="V85" s="41"/>
-      <c r="W85" s="2"/>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T85" s="40"/>
+      <c r="U85" s="40"/>
+      <c r="V85" s="40"/>
+      <c r="W85" s="40"/>
+      <c r="X85" s="2"/>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>59</v>
       </c>
@@ -7895,12 +7984,13 @@
       <c r="S86" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="T86" s="41"/>
-      <c r="U86" s="41"/>
-      <c r="V86" s="41"/>
-      <c r="W86" s="2"/>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T86" s="40"/>
+      <c r="U86" s="40"/>
+      <c r="V86" s="40"/>
+      <c r="W86" s="40"/>
+      <c r="X86" s="2"/>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>1016</v>
       </c>
@@ -7913,25 +8003,26 @@
       <c r="D87" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="E87" s="45"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
-      <c r="I87" s="45"/>
-      <c r="J87" s="45"/>
-      <c r="K87" s="45"/>
-      <c r="L87" s="45"/>
-      <c r="M87" s="45"/>
-      <c r="N87" s="45"/>
-      <c r="O87" s="45"/>
-      <c r="P87" s="45"/>
-      <c r="Q87" s="45"/>
-      <c r="T87" s="41"/>
-      <c r="U87" s="41"/>
-      <c r="V87" s="41"/>
-      <c r="W87" s="2"/>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="E87" s="44"/>
+      <c r="F87" s="44"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="44"/>
+      <c r="J87" s="44"/>
+      <c r="K87" s="44"/>
+      <c r="L87" s="44"/>
+      <c r="M87" s="44"/>
+      <c r="N87" s="44"/>
+      <c r="O87" s="44"/>
+      <c r="P87" s="44"/>
+      <c r="Q87" s="44"/>
+      <c r="T87" s="40"/>
+      <c r="U87" s="40"/>
+      <c r="V87" s="40"/>
+      <c r="W87" s="40"/>
+      <c r="X87" s="2"/>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>909</v>
       </c>
@@ -7947,12 +8038,13 @@
       <c r="E88" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="T88" s="41"/>
-      <c r="U88" s="41"/>
-      <c r="V88" s="41"/>
-      <c r="W88" s="2"/>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T88" s="40"/>
+      <c r="U88" s="40"/>
+      <c r="V88" s="40"/>
+      <c r="W88" s="40"/>
+      <c r="X88" s="2"/>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>60</v>
       </c>
@@ -8010,20 +8102,23 @@
       <c r="S89" s="11" t="s">
         <v>903</v>
       </c>
-      <c r="T89" s="44" t="s">
+      <c r="T89" s="43" t="s">
         <v>904</v>
       </c>
-      <c r="U89" s="44" t="s">
+      <c r="U89" s="43" t="s">
         <v>821</v>
       </c>
-      <c r="V89" s="44" t="s">
+      <c r="V89" s="43" t="s">
         <v>976</v>
       </c>
-      <c r="W89" s="51" t="s">
+      <c r="W89" s="41" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X89" s="2" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>61</v>
       </c>
@@ -8069,12 +8164,13 @@
       <c r="O90" s="1" t="s">
         <v>1061</v>
       </c>
-      <c r="T90" s="41"/>
-      <c r="U90" s="41"/>
-      <c r="V90" s="41"/>
-      <c r="W90" s="2"/>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T90" s="40"/>
+      <c r="U90" s="40"/>
+      <c r="V90" s="40"/>
+      <c r="W90" s="40"/>
+      <c r="X90" s="2"/>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>62</v>
       </c>
@@ -8132,12 +8228,13 @@
       <c r="S91" s="6" t="s">
         <v>1047</v>
       </c>
-      <c r="T91" s="41"/>
-      <c r="U91" s="41"/>
-      <c r="V91" s="41"/>
-      <c r="W91" s="2"/>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T91" s="40"/>
+      <c r="U91" s="40"/>
+      <c r="V91" s="40"/>
+      <c r="W91" s="40"/>
+      <c r="X91" s="2"/>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>921</v>
       </c>
@@ -8156,12 +8253,13 @@
       <c r="F92" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="T92" s="41"/>
-      <c r="U92" s="41"/>
-      <c r="V92" s="41"/>
-      <c r="W92" s="2"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T92" s="40"/>
+      <c r="U92" s="40"/>
+      <c r="V92" s="40"/>
+      <c r="W92" s="40"/>
+      <c r="X92" s="2"/>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>63</v>
       </c>
@@ -8210,12 +8308,13 @@
       <c r="P93" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="T93" s="41"/>
-      <c r="U93" s="41"/>
-      <c r="V93" s="41"/>
-      <c r="W93" s="2"/>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T93" s="40"/>
+      <c r="U93" s="40"/>
+      <c r="V93" s="40"/>
+      <c r="W93" s="40"/>
+      <c r="X93" s="2"/>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>64</v>
       </c>
@@ -8261,12 +8360,13 @@
       <c r="O94" s="10" t="s">
         <v>1029</v>
       </c>
-      <c r="T94" s="41"/>
-      <c r="U94" s="41"/>
-      <c r="V94" s="41"/>
-      <c r="W94" s="2"/>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T94" s="40"/>
+      <c r="U94" s="40"/>
+      <c r="V94" s="40"/>
+      <c r="W94" s="40"/>
+      <c r="X94" s="2"/>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>65</v>
       </c>
@@ -8306,12 +8406,13 @@
       <c r="M95" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="T95" s="41"/>
-      <c r="U95" s="41"/>
-      <c r="V95" s="41"/>
-      <c r="W95" s="2"/>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T95" s="40"/>
+      <c r="U95" s="40"/>
+      <c r="V95" s="40"/>
+      <c r="W95" s="40"/>
+      <c r="X95" s="2"/>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>138</v>
       </c>
@@ -8342,12 +8443,13 @@
       <c r="J96" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="T96" s="41"/>
-      <c r="U96" s="41"/>
-      <c r="V96" s="41"/>
-      <c r="W96" s="2"/>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T96" s="40"/>
+      <c r="U96" s="40"/>
+      <c r="V96" s="40"/>
+      <c r="W96" s="40"/>
+      <c r="X96" s="2"/>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>66</v>
       </c>
@@ -8402,12 +8504,13 @@
       <c r="R97" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="T97" s="41"/>
-      <c r="U97" s="41"/>
-      <c r="V97" s="41"/>
-      <c r="W97" s="2"/>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T97" s="40"/>
+      <c r="U97" s="40"/>
+      <c r="V97" s="40"/>
+      <c r="W97" s="40"/>
+      <c r="X97" s="2"/>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>879</v>
       </c>
@@ -8423,12 +8526,13 @@
       <c r="E98" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="T98" s="41"/>
-      <c r="U98" s="41"/>
-      <c r="V98" s="41"/>
-      <c r="W98" s="2"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T98" s="40"/>
+      <c r="U98" s="40"/>
+      <c r="V98" s="40"/>
+      <c r="W98" s="40"/>
+      <c r="X98" s="2"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>139</v>
       </c>
@@ -8465,12 +8569,13 @@
       <c r="L99" s="10" t="s">
         <v>893</v>
       </c>
-      <c r="T99" s="41"/>
-      <c r="U99" s="41"/>
-      <c r="V99" s="41"/>
-      <c r="W99" s="2"/>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T99" s="40"/>
+      <c r="U99" s="40"/>
+      <c r="V99" s="40"/>
+      <c r="W99" s="40"/>
+      <c r="X99" s="2"/>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>67</v>
       </c>
@@ -8513,12 +8618,13 @@
       <c r="N100" s="10" t="s">
         <v>889</v>
       </c>
-      <c r="T100" s="41"/>
-      <c r="U100" s="41"/>
-      <c r="V100" s="41"/>
-      <c r="W100" s="2"/>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T100" s="40"/>
+      <c r="U100" s="40"/>
+      <c r="V100" s="40"/>
+      <c r="W100" s="40"/>
+      <c r="X100" s="2"/>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>68</v>
       </c>
@@ -8558,12 +8664,13 @@
       <c r="M101" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="T101" s="41"/>
-      <c r="U101" s="41"/>
-      <c r="V101" s="41"/>
-      <c r="W101" s="2"/>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T101" s="40"/>
+      <c r="U101" s="40"/>
+      <c r="V101" s="40"/>
+      <c r="W101" s="40"/>
+      <c r="X101" s="2"/>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>69</v>
       </c>
@@ -8606,12 +8713,16 @@
       <c r="N102" s="7" t="s">
         <v>980</v>
       </c>
-      <c r="T102" s="41"/>
-      <c r="U102" s="41"/>
-      <c r="V102" s="41"/>
-      <c r="W102" s="2"/>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="O102" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="T102" s="40"/>
+      <c r="U102" s="40"/>
+      <c r="V102" s="40"/>
+      <c r="W102" s="40"/>
+      <c r="X102" s="2"/>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>140</v>
       </c>
@@ -8633,12 +8744,13 @@
       <c r="G103" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="T103" s="41"/>
-      <c r="U103" s="41"/>
-      <c r="V103" s="41"/>
-      <c r="W103" s="2"/>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T103" s="40"/>
+      <c r="U103" s="40"/>
+      <c r="V103" s="40"/>
+      <c r="W103" s="40"/>
+      <c r="X103" s="2"/>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>70</v>
       </c>
@@ -8684,12 +8796,13 @@
       <c r="O104" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="T104" s="41"/>
-      <c r="U104" s="41"/>
-      <c r="V104" s="41"/>
-      <c r="W104" s="2"/>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T104" s="40"/>
+      <c r="U104" s="40"/>
+      <c r="V104" s="40"/>
+      <c r="W104" s="40"/>
+      <c r="X104" s="2"/>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>71</v>
       </c>
@@ -8735,12 +8848,13 @@
       <c r="O105" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="T105" s="41"/>
-      <c r="U105" s="41"/>
-      <c r="V105" s="41"/>
-      <c r="W105" s="2"/>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T105" s="40"/>
+      <c r="U105" s="40"/>
+      <c r="V105" s="40"/>
+      <c r="W105" s="40"/>
+      <c r="X105" s="2"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>72</v>
       </c>
@@ -8783,12 +8897,13 @@
       <c r="N106" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="T106" s="41"/>
-      <c r="U106" s="41"/>
-      <c r="V106" s="41"/>
-      <c r="W106" s="2"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T106" s="40"/>
+      <c r="U106" s="40"/>
+      <c r="V106" s="40"/>
+      <c r="W106" s="40"/>
+      <c r="X106" s="2"/>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>73</v>
       </c>
@@ -8819,12 +8934,13 @@
       <c r="J107" s="9" t="s">
         <v>856</v>
       </c>
-      <c r="T107" s="41"/>
-      <c r="U107" s="41"/>
-      <c r="V107" s="41"/>
-      <c r="W107" s="2"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T107" s="40"/>
+      <c r="U107" s="40"/>
+      <c r="V107" s="40"/>
+      <c r="W107" s="40"/>
+      <c r="X107" s="2"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>74</v>
       </c>
@@ -8852,12 +8968,13 @@
       <c r="I108" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="T108" s="41"/>
-      <c r="U108" s="41"/>
-      <c r="V108" s="41"/>
-      <c r="W108" s="2"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T108" s="40"/>
+      <c r="U108" s="40"/>
+      <c r="V108" s="40"/>
+      <c r="W108" s="40"/>
+      <c r="X108" s="2"/>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>75</v>
       </c>
@@ -8900,12 +9017,13 @@
       <c r="N109" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="T109" s="41"/>
-      <c r="U109" s="41"/>
-      <c r="V109" s="41"/>
-      <c r="W109" s="2"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T109" s="40"/>
+      <c r="U109" s="40"/>
+      <c r="V109" s="40"/>
+      <c r="W109" s="40"/>
+      <c r="X109" s="2"/>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>76</v>
       </c>
@@ -8945,12 +9063,13 @@
       <c r="M110" s="10" t="s">
         <v>956</v>
       </c>
-      <c r="T110" s="41"/>
-      <c r="U110" s="41"/>
-      <c r="V110" s="41"/>
-      <c r="W110" s="2"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T110" s="40"/>
+      <c r="U110" s="40"/>
+      <c r="V110" s="40"/>
+      <c r="W110" s="40"/>
+      <c r="X110" s="2"/>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>77</v>
       </c>
@@ -8972,12 +9091,13 @@
       <c r="G111" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="T111" s="41"/>
-      <c r="U111" s="41"/>
-      <c r="V111" s="41"/>
-      <c r="W111" s="2"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T111" s="40"/>
+      <c r="U111" s="40"/>
+      <c r="V111" s="40"/>
+      <c r="W111" s="40"/>
+      <c r="X111" s="2"/>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>141</v>
       </c>
@@ -8996,12 +9116,13 @@
       <c r="F112" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="T112" s="41"/>
-      <c r="U112" s="41"/>
-      <c r="V112" s="41"/>
-      <c r="W112" s="2"/>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T112" s="40"/>
+      <c r="U112" s="40"/>
+      <c r="V112" s="40"/>
+      <c r="W112" s="40"/>
+      <c r="X112" s="2"/>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>838</v>
       </c>
@@ -9023,12 +9144,13 @@
       <c r="G113" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="T113" s="41"/>
-      <c r="U113" s="41"/>
-      <c r="V113" s="41"/>
-      <c r="W113" s="2"/>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T113" s="40"/>
+      <c r="U113" s="40"/>
+      <c r="V113" s="40"/>
+      <c r="W113" s="40"/>
+      <c r="X113" s="2"/>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>142</v>
       </c>
@@ -9080,12 +9202,13 @@
       <c r="Q114" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="T114" s="41"/>
-      <c r="U114" s="41"/>
-      <c r="V114" s="41"/>
-      <c r="W114" s="2"/>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T114" s="40"/>
+      <c r="U114" s="40"/>
+      <c r="V114" s="40"/>
+      <c r="W114" s="40"/>
+      <c r="X114" s="2"/>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>78</v>
       </c>
@@ -9116,12 +9239,16 @@
       <c r="J115" s="10" t="s">
         <v>930</v>
       </c>
-      <c r="T115" s="41"/>
-      <c r="U115" s="41"/>
-      <c r="V115" s="41"/>
-      <c r="W115" s="2"/>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="K115" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="T115" s="40"/>
+      <c r="U115" s="40"/>
+      <c r="V115" s="40"/>
+      <c r="W115" s="40"/>
+      <c r="X115" s="2"/>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>79</v>
       </c>
@@ -9176,12 +9303,13 @@
       <c r="R116" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="T116" s="41"/>
-      <c r="U116" s="41"/>
-      <c r="V116" s="41"/>
-      <c r="W116" s="2"/>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T116" s="40"/>
+      <c r="U116" s="40"/>
+      <c r="V116" s="40"/>
+      <c r="W116" s="40"/>
+      <c r="X116" s="2"/>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>143</v>
       </c>
@@ -9206,12 +9334,13 @@
       <c r="H117" s="13" t="s">
         <v>819</v>
       </c>
-      <c r="T117" s="41"/>
-      <c r="U117" s="41"/>
-      <c r="V117" s="41"/>
-      <c r="W117" s="2"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T117" s="40"/>
+      <c r="U117" s="40"/>
+      <c r="V117" s="40"/>
+      <c r="W117" s="40"/>
+      <c r="X117" s="2"/>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>80</v>
       </c>
@@ -9260,12 +9389,13 @@
       <c r="P118" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="T118" s="41"/>
-      <c r="U118" s="41"/>
-      <c r="V118" s="41"/>
-      <c r="W118" s="2"/>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T118" s="40"/>
+      <c r="U118" s="40"/>
+      <c r="V118" s="40"/>
+      <c r="W118" s="40"/>
+      <c r="X118" s="2"/>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>144</v>
       </c>
@@ -9290,12 +9420,13 @@
       <c r="H119" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="T119" s="41"/>
-      <c r="U119" s="41"/>
-      <c r="V119" s="41"/>
-      <c r="W119" s="2"/>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T119" s="40"/>
+      <c r="U119" s="40"/>
+      <c r="V119" s="40"/>
+      <c r="W119" s="40"/>
+      <c r="X119" s="2"/>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>81</v>
       </c>
@@ -9341,12 +9472,13 @@
       <c r="O120" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="T120" s="41"/>
-      <c r="U120" s="41"/>
-      <c r="V120" s="41"/>
-      <c r="W120" s="2"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T120" s="40"/>
+      <c r="U120" s="40"/>
+      <c r="V120" s="40"/>
+      <c r="W120" s="40"/>
+      <c r="X120" s="2"/>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>145</v>
       </c>
@@ -9386,12 +9518,13 @@
       <c r="M121" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="T121" s="41"/>
-      <c r="U121" s="41"/>
-      <c r="V121" s="41"/>
-      <c r="W121" s="2"/>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T121" s="40"/>
+      <c r="U121" s="40"/>
+      <c r="V121" s="40"/>
+      <c r="W121" s="40"/>
+      <c r="X121" s="2"/>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>82</v>
       </c>
@@ -9428,12 +9561,19 @@
       <c r="L122" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="T122" s="41"/>
-      <c r="U122" s="41"/>
-      <c r="V122" s="41"/>
-      <c r="W122" s="2"/>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="M122" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="T122" s="40"/>
+      <c r="U122" s="40"/>
+      <c r="V122" s="40"/>
+      <c r="W122" s="40"/>
+      <c r="X122" s="2"/>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>83</v>
       </c>
@@ -9470,12 +9610,13 @@
       <c r="L123" s="9" t="s">
         <v>1032</v>
       </c>
-      <c r="T123" s="41"/>
-      <c r="U123" s="41"/>
-      <c r="V123" s="41"/>
-      <c r="W123" s="2"/>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T123" s="40"/>
+      <c r="U123" s="40"/>
+      <c r="V123" s="40"/>
+      <c r="W123" s="40"/>
+      <c r="X123" s="2"/>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>84</v>
       </c>
@@ -9530,12 +9671,13 @@
       <c r="R124" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="T124" s="41"/>
-      <c r="U124" s="41"/>
-      <c r="V124" s="41"/>
-      <c r="W124" s="2"/>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T124" s="40"/>
+      <c r="U124" s="40"/>
+      <c r="V124" s="40"/>
+      <c r="W124" s="40"/>
+      <c r="X124" s="2"/>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>85</v>
       </c>
@@ -9581,25 +9723,26 @@
       <c r="O125" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="T125" s="41"/>
-      <c r="U125" s="41"/>
-      <c r="V125" s="41"/>
-      <c r="W125" s="2"/>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T125" s="40"/>
+      <c r="U125" s="40"/>
+      <c r="V125" s="40"/>
+      <c r="W125" s="40"/>
+      <c r="X125" s="2"/>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B126" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C126" s="45" t="s">
+      <c r="B126" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C126" s="44" t="s">
         <v>1058</v>
       </c>
-      <c r="D126" s="45" t="s">
+      <c r="D126" s="44" t="s">
         <v>639</v>
       </c>
-      <c r="E126" s="45" t="s">
+      <c r="E126" s="44" t="s">
         <v>640</v>
       </c>
       <c r="F126" s="6" t="s">
@@ -9617,12 +9760,13 @@
       <c r="J126" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="T126" s="41"/>
-      <c r="U126" s="41"/>
-      <c r="V126" s="41"/>
-      <c r="W126" s="2"/>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T126" s="40"/>
+      <c r="U126" s="40"/>
+      <c r="V126" s="40"/>
+      <c r="W126" s="40"/>
+      <c r="X126" s="2"/>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>87</v>
       </c>
@@ -9665,12 +9809,13 @@
       <c r="N127" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="T127" s="41"/>
-      <c r="U127" s="41"/>
-      <c r="V127" s="41"/>
-      <c r="W127" s="2"/>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T127" s="40"/>
+      <c r="U127" s="40"/>
+      <c r="V127" s="40"/>
+      <c r="W127" s="40"/>
+      <c r="X127" s="2"/>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>88</v>
       </c>
@@ -9710,12 +9855,13 @@
       <c r="M128" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="T128" s="41"/>
-      <c r="U128" s="41"/>
-      <c r="V128" s="41"/>
-      <c r="W128" s="2"/>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T128" s="40"/>
+      <c r="U128" s="40"/>
+      <c r="V128" s="40"/>
+      <c r="W128" s="40"/>
+      <c r="X128" s="2"/>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>89</v>
       </c>
@@ -9773,16 +9919,17 @@
       <c r="S129" s="9" t="s">
         <v>944</v>
       </c>
-      <c r="T129" s="47" t="s">
+      <c r="T129" s="46" t="s">
         <v>993</v>
       </c>
-      <c r="U129" s="41" t="s">
+      <c r="U129" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="V129" s="41"/>
-      <c r="W129" s="2"/>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V129" s="40"/>
+      <c r="W129" s="40"/>
+      <c r="X129" s="2"/>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>146</v>
       </c>
@@ -9807,12 +9954,13 @@
       <c r="H130" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="T130" s="41"/>
-      <c r="U130" s="41"/>
-      <c r="V130" s="41"/>
-      <c r="W130" s="2"/>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T130" s="40"/>
+      <c r="U130" s="40"/>
+      <c r="V130" s="40"/>
+      <c r="W130" s="40"/>
+      <c r="X130" s="2"/>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>946</v>
       </c>
@@ -9825,12 +9973,13 @@
       <c r="D131" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="T131" s="41"/>
-      <c r="U131" s="41"/>
-      <c r="V131" s="41"/>
-      <c r="W131" s="2"/>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T131" s="40"/>
+      <c r="U131" s="40"/>
+      <c r="V131" s="40"/>
+      <c r="W131" s="40"/>
+      <c r="X131" s="2"/>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>90</v>
       </c>
@@ -9885,12 +10034,13 @@
       <c r="R132" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="T132" s="41"/>
-      <c r="U132" s="41"/>
-      <c r="V132" s="41"/>
-      <c r="W132" s="2"/>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T132" s="40"/>
+      <c r="U132" s="40"/>
+      <c r="V132" s="40"/>
+      <c r="W132" s="40"/>
+      <c r="X132" s="2"/>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>91</v>
       </c>
@@ -9948,12 +10098,15 @@
       <c r="S133" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="T133" s="41"/>
-      <c r="U133" s="41"/>
-      <c r="V133" s="41"/>
-      <c r="W133" s="2"/>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T133" s="40" t="s">
+        <v>875</v>
+      </c>
+      <c r="U133" s="40"/>
+      <c r="V133" s="40"/>
+      <c r="W133" s="40"/>
+      <c r="X133" s="2"/>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>147</v>
       </c>
@@ -9990,12 +10143,13 @@
       <c r="L134" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="T134" s="41"/>
-      <c r="U134" s="41"/>
-      <c r="V134" s="41"/>
-      <c r="W134" s="2"/>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T134" s="40"/>
+      <c r="U134" s="40"/>
+      <c r="V134" s="40"/>
+      <c r="W134" s="40"/>
+      <c r="X134" s="2"/>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>92</v>
       </c>
@@ -10029,12 +10183,13 @@
       <c r="K135" s="9" t="s">
         <v>981</v>
       </c>
-      <c r="T135" s="41"/>
-      <c r="U135" s="41"/>
-      <c r="V135" s="41"/>
-      <c r="W135" s="2"/>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T135" s="40"/>
+      <c r="U135" s="40"/>
+      <c r="V135" s="40"/>
+      <c r="W135" s="40"/>
+      <c r="X135" s="2"/>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>93</v>
       </c>
@@ -10080,12 +10235,13 @@
       <c r="O136" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="T136" s="41"/>
-      <c r="U136" s="41"/>
-      <c r="V136" s="41"/>
-      <c r="W136" s="2"/>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T136" s="40"/>
+      <c r="U136" s="40"/>
+      <c r="V136" s="40"/>
+      <c r="W136" s="40"/>
+      <c r="X136" s="2"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>94</v>
       </c>
@@ -10113,12 +10269,13 @@
       <c r="I137" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="T137" s="41"/>
-      <c r="U137" s="41"/>
-      <c r="V137" s="41"/>
-      <c r="W137" s="2"/>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T137" s="40"/>
+      <c r="U137" s="40"/>
+      <c r="V137" s="40"/>
+      <c r="W137" s="40"/>
+      <c r="X137" s="2"/>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>95</v>
       </c>
@@ -10143,12 +10300,13 @@
       <c r="H138" s="6" t="s">
         <v>1049</v>
       </c>
-      <c r="T138" s="41"/>
-      <c r="U138" s="41"/>
-      <c r="V138" s="41"/>
-      <c r="W138" s="2"/>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T138" s="40"/>
+      <c r="U138" s="40"/>
+      <c r="V138" s="40"/>
+      <c r="W138" s="40"/>
+      <c r="X138" s="2"/>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>96</v>
       </c>
@@ -10191,12 +10349,13 @@
       <c r="N139" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="T139" s="41"/>
-      <c r="U139" s="41"/>
-      <c r="V139" s="41"/>
-      <c r="W139" s="2"/>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T139" s="40"/>
+      <c r="U139" s="40"/>
+      <c r="V139" s="40"/>
+      <c r="W139" s="40"/>
+      <c r="X139" s="2"/>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>148</v>
       </c>
@@ -10224,12 +10383,13 @@
       <c r="I140" s="10" t="s">
         <v>1028</v>
       </c>
-      <c r="T140" s="41"/>
-      <c r="U140" s="41"/>
-      <c r="V140" s="41"/>
-      <c r="W140" s="2"/>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T140" s="40"/>
+      <c r="U140" s="40"/>
+      <c r="V140" s="40"/>
+      <c r="W140" s="40"/>
+      <c r="X140" s="2"/>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>97</v>
       </c>
@@ -10281,12 +10441,13 @@
       <c r="Q141" s="6" t="s">
         <v>1032</v>
       </c>
-      <c r="T141" s="41"/>
-      <c r="U141" s="41"/>
-      <c r="V141" s="41"/>
-      <c r="W141" s="2"/>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T141" s="40"/>
+      <c r="U141" s="40"/>
+      <c r="V141" s="40"/>
+      <c r="W141" s="40"/>
+      <c r="X141" s="2"/>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>98</v>
       </c>
@@ -10338,12 +10499,13 @@
       <c r="Q142" s="10" t="s">
         <v>985</v>
       </c>
-      <c r="T142" s="41"/>
-      <c r="U142" s="41"/>
-      <c r="V142" s="41"/>
-      <c r="W142" s="2"/>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T142" s="40"/>
+      <c r="U142" s="40"/>
+      <c r="V142" s="40"/>
+      <c r="W142" s="40"/>
+      <c r="X142" s="2"/>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>99</v>
       </c>
@@ -10398,12 +10560,18 @@
       <c r="R143" s="10" t="s">
         <v>970</v>
       </c>
-      <c r="T143" s="41"/>
-      <c r="U143" s="41"/>
-      <c r="V143" s="41"/>
-      <c r="W143" s="2"/>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="S143" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="T143" s="40" t="s">
+        <v>969</v>
+      </c>
+      <c r="U143" s="40"/>
+      <c r="V143" s="40"/>
+      <c r="W143" s="40"/>
+      <c r="X143" s="2"/>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>100</v>
       </c>
@@ -10434,12 +10602,13 @@
       <c r="J144" s="13" t="s">
         <v>991</v>
       </c>
-      <c r="T144" s="41"/>
-      <c r="U144" s="41"/>
-      <c r="V144" s="41"/>
-      <c r="W144" s="2"/>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T144" s="40"/>
+      <c r="U144" s="40"/>
+      <c r="V144" s="40"/>
+      <c r="W144" s="40"/>
+      <c r="X144" s="2"/>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>101</v>
       </c>
@@ -10485,12 +10654,13 @@
       <c r="O145" s="9" t="s">
         <v>1038</v>
       </c>
-      <c r="T145" s="41"/>
-      <c r="U145" s="41"/>
-      <c r="V145" s="41"/>
-      <c r="W145" s="2"/>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T145" s="40"/>
+      <c r="U145" s="40"/>
+      <c r="V145" s="40"/>
+      <c r="W145" s="40"/>
+      <c r="X145" s="2"/>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>102</v>
       </c>
@@ -10545,12 +10715,13 @@
       <c r="R146" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="T146" s="41"/>
-      <c r="U146" s="41"/>
-      <c r="V146" s="41"/>
-      <c r="W146" s="2"/>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T146" s="40"/>
+      <c r="U146" s="40"/>
+      <c r="V146" s="40"/>
+      <c r="W146" s="40"/>
+      <c r="X146" s="2"/>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>103</v>
       </c>
@@ -10599,12 +10770,13 @@
       <c r="P147" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="T147" s="41"/>
-      <c r="U147" s="41"/>
-      <c r="V147" s="41"/>
-      <c r="W147" s="2"/>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T147" s="40"/>
+      <c r="U147" s="40"/>
+      <c r="V147" s="40"/>
+      <c r="W147" s="40"/>
+      <c r="X147" s="2"/>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>104</v>
       </c>
@@ -10629,12 +10801,13 @@
       <c r="H148" s="10" t="s">
         <v>915</v>
       </c>
-      <c r="T148" s="41"/>
-      <c r="U148" s="41"/>
-      <c r="V148" s="41"/>
-      <c r="W148" s="2"/>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T148" s="40"/>
+      <c r="U148" s="40"/>
+      <c r="V148" s="40"/>
+      <c r="W148" s="40"/>
+      <c r="X148" s="2"/>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>105</v>
       </c>
@@ -10662,12 +10835,13 @@
       <c r="I149" s="12" t="s">
         <v>1023</v>
       </c>
-      <c r="T149" s="41"/>
-      <c r="U149" s="41"/>
-      <c r="V149" s="41"/>
-      <c r="W149" s="2"/>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T149" s="40"/>
+      <c r="U149" s="40"/>
+      <c r="V149" s="40"/>
+      <c r="W149" s="40"/>
+      <c r="X149" s="2"/>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>106</v>
       </c>
@@ -10719,12 +10893,13 @@
       <c r="Q150" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="T150" s="41"/>
-      <c r="U150" s="41"/>
-      <c r="V150" s="41"/>
-      <c r="W150" s="2"/>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T150" s="40"/>
+      <c r="U150" s="40"/>
+      <c r="V150" s="40"/>
+      <c r="W150" s="40"/>
+      <c r="X150" s="2"/>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>107</v>
       </c>
@@ -10782,14 +10957,15 @@
       <c r="S151" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="T151" s="41" t="s">
+      <c r="T151" s="40" t="s">
         <v>1066</v>
       </c>
-      <c r="U151" s="41"/>
-      <c r="V151" s="41"/>
-      <c r="W151" s="2"/>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U151" s="40"/>
+      <c r="V151" s="40"/>
+      <c r="W151" s="40"/>
+      <c r="X151" s="2"/>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>108</v>
       </c>
@@ -10841,12 +11017,16 @@
       <c r="Q152" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="T152" s="41"/>
-      <c r="U152" s="41"/>
-      <c r="V152" s="41"/>
-      <c r="W152" s="2"/>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="R152" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="T152" s="40"/>
+      <c r="U152" s="40"/>
+      <c r="V152" s="40"/>
+      <c r="W152" s="40"/>
+      <c r="X152" s="2"/>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>109</v>
       </c>
@@ -10874,12 +11054,13 @@
       <c r="I153" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="T153" s="41"/>
-      <c r="U153" s="41"/>
-      <c r="V153" s="41"/>
-      <c r="W153" s="2"/>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T153" s="40"/>
+      <c r="U153" s="40"/>
+      <c r="V153" s="40"/>
+      <c r="W153" s="40"/>
+      <c r="X153" s="2"/>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>810</v>
       </c>
@@ -10898,12 +11079,13 @@
       <c r="F154" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="T154" s="41"/>
-      <c r="U154" s="41"/>
-      <c r="V154" s="41"/>
-      <c r="W154" s="2"/>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T154" s="40"/>
+      <c r="U154" s="40"/>
+      <c r="V154" s="40"/>
+      <c r="W154" s="40"/>
+      <c r="X154" s="2"/>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>110</v>
       </c>
@@ -10949,12 +11131,13 @@
       <c r="O155" s="10" t="s">
         <v>980</v>
       </c>
-      <c r="T155" s="41"/>
-      <c r="U155" s="41"/>
-      <c r="V155" s="41"/>
-      <c r="W155" s="2"/>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T155" s="40"/>
+      <c r="U155" s="40"/>
+      <c r="V155" s="40"/>
+      <c r="W155" s="40"/>
+      <c r="X155" s="2"/>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>149</v>
       </c>
@@ -10982,12 +11165,13 @@
       <c r="I156" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="T156" s="41"/>
-      <c r="U156" s="41"/>
-      <c r="V156" s="41"/>
-      <c r="W156" s="2"/>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T156" s="40"/>
+      <c r="U156" s="40"/>
+      <c r="V156" s="40"/>
+      <c r="W156" s="40"/>
+      <c r="X156" s="2"/>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>111</v>
       </c>
@@ -11018,12 +11202,13 @@
       <c r="J157" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="T157" s="41"/>
-      <c r="U157" s="41"/>
-      <c r="V157" s="41"/>
-      <c r="W157" s="2"/>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T157" s="40"/>
+      <c r="U157" s="40"/>
+      <c r="V157" s="40"/>
+      <c r="W157" s="40"/>
+      <c r="X157" s="2"/>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>150</v>
       </c>
@@ -11072,12 +11257,13 @@
       <c r="P158" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="T158" s="41"/>
-      <c r="U158" s="41"/>
-      <c r="V158" s="41"/>
-      <c r="W158" s="2"/>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T158" s="40"/>
+      <c r="U158" s="40"/>
+      <c r="V158" s="40"/>
+      <c r="W158" s="40"/>
+      <c r="X158" s="2"/>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>112</v>
       </c>
@@ -11114,12 +11300,13 @@
       <c r="L159" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="T159" s="41"/>
-      <c r="U159" s="41"/>
-      <c r="V159" s="41"/>
-      <c r="W159" s="2"/>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T159" s="40"/>
+      <c r="U159" s="40"/>
+      <c r="V159" s="40"/>
+      <c r="W159" s="40"/>
+      <c r="X159" s="2"/>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>113</v>
       </c>
@@ -11174,12 +11361,13 @@
       <c r="R160" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="T160" s="41"/>
-      <c r="U160" s="41"/>
-      <c r="V160" s="41"/>
-      <c r="W160" s="2"/>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T160" s="40"/>
+      <c r="U160" s="40"/>
+      <c r="V160" s="40"/>
+      <c r="W160" s="40"/>
+      <c r="X160" s="2"/>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>151</v>
       </c>
@@ -11213,12 +11401,13 @@
       <c r="K161" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="T161" s="41"/>
-      <c r="U161" s="41"/>
-      <c r="V161" s="41"/>
-      <c r="W161" s="2"/>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T161" s="40"/>
+      <c r="U161" s="40"/>
+      <c r="V161" s="40"/>
+      <c r="W161" s="40"/>
+      <c r="X161" s="2"/>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>114</v>
       </c>
@@ -11261,12 +11450,13 @@
       <c r="N162" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="T162" s="41"/>
-      <c r="U162" s="41"/>
-      <c r="V162" s="41"/>
-      <c r="W162" s="2"/>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T162" s="40"/>
+      <c r="U162" s="40"/>
+      <c r="V162" s="40"/>
+      <c r="W162" s="40"/>
+      <c r="X162" s="2"/>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>115</v>
       </c>
@@ -11300,12 +11490,13 @@
       <c r="K163" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="T163" s="41"/>
-      <c r="U163" s="41"/>
-      <c r="V163" s="41"/>
-      <c r="W163" s="2"/>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T163" s="40"/>
+      <c r="U163" s="40"/>
+      <c r="V163" s="40"/>
+      <c r="W163" s="40"/>
+      <c r="X163" s="2"/>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>116</v>
       </c>
@@ -11345,12 +11536,16 @@
       <c r="M164" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="T164" s="41"/>
-      <c r="U164" s="41"/>
-      <c r="V164" s="41"/>
-      <c r="W164" s="2"/>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N164" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="T164" s="40"/>
+      <c r="U164" s="40"/>
+      <c r="V164" s="40"/>
+      <c r="W164" s="40"/>
+      <c r="X164" s="2"/>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>117</v>
       </c>
@@ -11408,14 +11603,15 @@
       <c r="S165" s="8" t="s">
         <v>992</v>
       </c>
-      <c r="T165" s="44" t="s">
+      <c r="T165" s="43" t="s">
         <v>1052</v>
       </c>
-      <c r="U165" s="41"/>
-      <c r="V165" s="41"/>
-      <c r="W165" s="2"/>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U165" s="40"/>
+      <c r="V165" s="40"/>
+      <c r="W165" s="40"/>
+      <c r="X165" s="2"/>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>152</v>
       </c>
@@ -11455,12 +11651,13 @@
       <c r="M166" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="T166" s="41"/>
-      <c r="U166" s="41"/>
-      <c r="V166" s="41"/>
-      <c r="W166" s="2"/>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T166" s="40"/>
+      <c r="U166" s="40"/>
+      <c r="V166" s="40"/>
+      <c r="W166" s="40"/>
+      <c r="X166" s="2"/>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>118</v>
       </c>
@@ -11494,12 +11691,13 @@
       <c r="K167" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="T167" s="41"/>
-      <c r="U167" s="41"/>
-      <c r="V167" s="41"/>
-      <c r="W167" s="2"/>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T167" s="40"/>
+      <c r="U167" s="40"/>
+      <c r="V167" s="40"/>
+      <c r="W167" s="40"/>
+      <c r="X167" s="2"/>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>1031</v>
       </c>
@@ -11509,19 +11707,22 @@
       <c r="C168" s="10" t="s">
         <v>1032</v>
       </c>
-      <c r="D168" s="45"/>
-      <c r="E168" s="45"/>
-      <c r="F168" s="45"/>
-      <c r="G168" s="45"/>
-      <c r="H168" s="45"/>
-      <c r="I168" s="45"/>
-      <c r="J168" s="45"/>
-      <c r="T168" s="41"/>
-      <c r="U168" s="41"/>
-      <c r="V168" s="41"/>
-      <c r="W168" s="2"/>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D168" s="44" t="s">
+        <v>980</v>
+      </c>
+      <c r="E168" s="44"/>
+      <c r="F168" s="44"/>
+      <c r="G168" s="44"/>
+      <c r="H168" s="44"/>
+      <c r="I168" s="44"/>
+      <c r="J168" s="44"/>
+      <c r="T168" s="40"/>
+      <c r="U168" s="40"/>
+      <c r="V168" s="40"/>
+      <c r="W168" s="40"/>
+      <c r="X168" s="2"/>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>119</v>
       </c>
@@ -11558,12 +11759,13 @@
       <c r="L169" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="T169" s="41"/>
-      <c r="U169" s="41"/>
-      <c r="V169" s="41"/>
-      <c r="W169" s="2"/>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T169" s="40"/>
+      <c r="U169" s="40"/>
+      <c r="V169" s="40"/>
+      <c r="W169" s="40"/>
+      <c r="X169" s="2"/>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>1045</v>
       </c>
@@ -11573,19 +11775,20 @@
       <c r="C170" s="11" t="s">
         <v>923</v>
       </c>
-      <c r="D170" s="45"/>
-      <c r="E170" s="45"/>
-      <c r="F170" s="45"/>
-      <c r="G170" s="45"/>
-      <c r="H170" s="45"/>
-      <c r="I170" s="45"/>
-      <c r="J170" s="45"/>
-      <c r="T170" s="41"/>
-      <c r="U170" s="41"/>
-      <c r="V170" s="41"/>
-      <c r="W170" s="2"/>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D170" s="44"/>
+      <c r="E170" s="44"/>
+      <c r="F170" s="44"/>
+      <c r="G170" s="44"/>
+      <c r="H170" s="44"/>
+      <c r="I170" s="44"/>
+      <c r="J170" s="44"/>
+      <c r="T170" s="40"/>
+      <c r="U170" s="40"/>
+      <c r="V170" s="40"/>
+      <c r="W170" s="40"/>
+      <c r="X170" s="2"/>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>154</v>
       </c>
@@ -11613,12 +11816,13 @@
       <c r="I171" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="T171" s="41"/>
-      <c r="U171" s="41"/>
-      <c r="V171" s="41"/>
-      <c r="W171" s="2"/>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T171" s="40"/>
+      <c r="U171" s="40"/>
+      <c r="V171" s="40"/>
+      <c r="W171" s="40"/>
+      <c r="X171" s="2"/>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>120</v>
       </c>
@@ -11667,12 +11871,13 @@
       <c r="P172" s="10" t="s">
         <v>869</v>
       </c>
-      <c r="T172" s="41"/>
-      <c r="U172" s="41"/>
-      <c r="V172" s="41"/>
-      <c r="W172" s="2"/>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T172" s="40"/>
+      <c r="U172" s="40"/>
+      <c r="V172" s="40"/>
+      <c r="W172" s="40"/>
+      <c r="X172" s="2"/>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>822</v>
       </c>
@@ -11697,12 +11902,13 @@
       <c r="H173" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="T173" s="41"/>
-      <c r="U173" s="41"/>
-      <c r="V173" s="41"/>
-      <c r="W173" s="2"/>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T173" s="40"/>
+      <c r="U173" s="40"/>
+      <c r="V173" s="40"/>
+      <c r="W173" s="40"/>
+      <c r="X173" s="2"/>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>121</v>
       </c>
@@ -11745,12 +11951,13 @@
       <c r="N174" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="T174" s="41"/>
-      <c r="U174" s="41"/>
-      <c r="V174" s="41"/>
-      <c r="W174" s="2"/>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T174" s="40"/>
+      <c r="U174" s="40"/>
+      <c r="V174" s="40"/>
+      <c r="W174" s="40"/>
+      <c r="X174" s="2"/>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>122</v>
       </c>
@@ -11781,12 +11988,13 @@
       <c r="J175" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="T175" s="41"/>
-      <c r="U175" s="41"/>
-      <c r="V175" s="41"/>
-      <c r="W175" s="2"/>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T175" s="40"/>
+      <c r="U175" s="40"/>
+      <c r="V175" s="40"/>
+      <c r="W175" s="40"/>
+      <c r="X175" s="2"/>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>153</v>
       </c>
@@ -11820,12 +12028,13 @@
       <c r="K176" s="6" t="s">
         <v>1042</v>
       </c>
-      <c r="T176" s="41"/>
-      <c r="U176" s="41"/>
-      <c r="V176" s="41"/>
-      <c r="W176" s="2"/>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T176" s="40"/>
+      <c r="U176" s="40"/>
+      <c r="V176" s="40"/>
+      <c r="W176" s="40"/>
+      <c r="X176" s="2"/>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>123</v>
       </c>
@@ -11862,10 +12071,10 @@
       <c r="L177" s="16" t="s">
         <v>930</v>
       </c>
-      <c r="M177" s="52" t="s">
+      <c r="M177" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="N177" s="52" t="s">
+      <c r="N177" s="49" t="s">
         <v>173</v>
       </c>
       <c r="O177" s="3"/>
@@ -11876,7 +12085,8 @@
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
       <c r="V177" s="3"/>
-      <c r="W177" s="4"/>
+      <c r="W177" s="3"/>
+      <c r="X177" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="1080">
   <si>
     <t>Aatrox</t>
   </si>
@@ -4456,6 +4456,9 @@
       <c r="N12" s="5" t="s">
         <v>162</v>
       </c>
+      <c r="O12" s="1" t="s">
+        <v>803</v>
+      </c>
       <c r="T12" s="40"/>
       <c r="U12" s="40"/>
       <c r="V12" s="40"/>
@@ -6402,6 +6405,9 @@
       </c>
       <c r="Q54" s="6" t="s">
         <v>947</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="T54" s="40"/>
       <c r="U54" s="40"/>
@@ -8003,7 +8009,9 @@
       <c r="D87" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="E87" s="44"/>
+      <c r="E87" s="44" t="s">
+        <v>276</v>
+      </c>
       <c r="F87" s="44"/>
       <c r="G87" s="44"/>
       <c r="H87" s="44"/>
@@ -10835,6 +10843,9 @@
       <c r="I149" s="12" t="s">
         <v>1023</v>
       </c>
+      <c r="J149" s="1" t="s">
+        <v>803</v>
+      </c>
       <c r="T149" s="40"/>
       <c r="U149" s="40"/>
       <c r="V149" s="40"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="1083">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3264,13 +3264,22 @@
   </si>
   <si>
     <t>Heartsong</t>
+  </si>
+  <si>
+    <t>Prestige HEARTSTEEL Live My Life</t>
+  </si>
+  <si>
+    <t>Heartsteel Live My Life</t>
+  </si>
+  <si>
+    <t>Prestige Classic Baron</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3287,6 +3296,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3614,9 +3630,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3633,6 +3646,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3970,7 +3986,9 @@
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="7" width="25.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="28" style="1" customWidth="1"/>
-    <col min="9" max="16" width="25.7109375" style="1" customWidth="1"/>
+    <col min="9" max="12" width="25.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="30.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16" width="25.7109375" style="1" customWidth="1"/>
     <col min="17" max="17" width="27" style="1" customWidth="1"/>
     <col min="18" max="19" width="25.7109375" style="1" customWidth="1"/>
     <col min="20" max="20" width="30.7109375" style="1" customWidth="1"/>
@@ -4032,24 +4050,24 @@
       <c r="A4" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="50"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
       <c r="R4" s="38"/>
       <c r="S4" s="3"/>
       <c r="T4" s="37"/>
@@ -4163,13 +4181,13 @@
       <c r="S6" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="T6" s="47" t="s">
+      <c r="T6" s="46" t="s">
         <v>969</v>
       </c>
       <c r="U6" s="43" t="s">
         <v>1032</v>
       </c>
-      <c r="V6" s="46" t="s">
+      <c r="V6" s="45" t="s">
         <v>1033</v>
       </c>
       <c r="W6" s="40"/>
@@ -4236,7 +4254,7 @@
       <c r="T7" s="41" t="s">
         <v>855</v>
       </c>
-      <c r="U7" s="46" t="s">
+      <c r="U7" s="45" t="s">
         <v>893</v>
       </c>
       <c r="V7" s="41" t="s">
@@ -4556,6 +4574,9 @@
       <c r="H14" s="6" t="s">
         <v>1034</v>
       </c>
+      <c r="I14" s="40" t="s">
+        <v>1081</v>
+      </c>
       <c r="T14" s="40"/>
       <c r="U14" s="40"/>
       <c r="V14" s="40"/>
@@ -4620,13 +4641,13 @@
       <c r="S15" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="T15" s="46" t="s">
+      <c r="T15" s="45" t="s">
         <v>177</v>
       </c>
       <c r="U15" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="V15" s="48" t="s">
+      <c r="V15" s="47" t="s">
         <v>432</v>
       </c>
       <c r="W15" s="40"/>
@@ -5012,7 +5033,7 @@
       <c r="S25" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="T25" s="46" t="s">
+      <c r="T25" s="45" t="s">
         <v>1001</v>
       </c>
       <c r="U25" s="43" t="s">
@@ -5619,13 +5640,15 @@
       <c r="U37" s="43" t="s">
         <v>947</v>
       </c>
-      <c r="V37" s="48" t="s">
+      <c r="V37" s="47" t="s">
         <v>949</v>
       </c>
-      <c r="W37" s="46" t="s">
+      <c r="W37" s="45" t="s">
         <v>1014</v>
       </c>
-      <c r="X37" s="2"/>
+      <c r="X37" s="2" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
@@ -6981,10 +7004,10 @@
       <c r="S65" s="5" t="s">
         <v>996</v>
       </c>
-      <c r="T65" s="47" t="s">
+      <c r="T65" s="46" t="s">
         <v>1015</v>
       </c>
-      <c r="U65" s="47" t="s">
+      <c r="U65" s="46" t="s">
         <v>1052</v>
       </c>
       <c r="V65" s="40"/>
@@ -7083,6 +7106,9 @@
       <c r="I67" s="10" t="s">
         <v>274</v>
       </c>
+      <c r="J67" s="40" t="s">
+        <v>1081</v>
+      </c>
       <c r="T67" s="40"/>
       <c r="U67" s="40"/>
       <c r="V67" s="40"/>
@@ -7286,7 +7312,9 @@
       <c r="Q72" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R72" s="45"/>
+      <c r="R72" s="51" t="s">
+        <v>1082</v>
+      </c>
       <c r="T72" s="40"/>
       <c r="U72" s="40"/>
       <c r="V72" s="40"/>
@@ -7309,6 +7337,10 @@
       <c r="E73" s="11" t="s">
         <v>935</v>
       </c>
+      <c r="F73" s="40" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G73" s="40"/>
       <c r="T73" s="40"/>
       <c r="U73" s="40"/>
       <c r="V73" s="40"/>
@@ -7768,13 +7800,13 @@
       <c r="T82" s="7" t="s">
         <v>920</v>
       </c>
-      <c r="U82" s="46" t="s">
+      <c r="U82" s="45" t="s">
         <v>906</v>
       </c>
-      <c r="V82" s="47" t="s">
+      <c r="V82" s="46" t="s">
         <v>869</v>
       </c>
-      <c r="W82" s="47" t="s">
+      <c r="W82" s="46" t="s">
         <v>1043</v>
       </c>
       <c r="X82" s="2"/>
@@ -9618,6 +9650,9 @@
       <c r="L123" s="9" t="s">
         <v>1032</v>
       </c>
+      <c r="M123" s="1" t="s">
+        <v>1080</v>
+      </c>
       <c r="T123" s="40"/>
       <c r="U123" s="40"/>
       <c r="V123" s="40"/>
@@ -9927,7 +9962,7 @@
       <c r="S129" s="9" t="s">
         <v>944</v>
       </c>
-      <c r="T129" s="46" t="s">
+      <c r="T129" s="45" t="s">
         <v>993</v>
       </c>
       <c r="U129" s="40" t="s">
@@ -11661,6 +11696,9 @@
       </c>
       <c r="M166" s="6" t="s">
         <v>980</v>
+      </c>
+      <c r="N166" s="40" t="s">
+        <v>1081</v>
       </c>
       <c r="T166" s="40"/>
       <c r="U166" s="40"/>
@@ -12082,10 +12120,10 @@
       <c r="L177" s="16" t="s">
         <v>930</v>
       </c>
-      <c r="M177" s="49" t="s">
+      <c r="M177" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="N177" s="49" t="s">
+      <c r="N177" s="48" t="s">
         <v>173</v>
       </c>
       <c r="O177" s="3"/>

--- a/src/assets/resources/Tierlist.xlsx
+++ b/src/assets/resources/Tierlist.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2293" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2298" uniqueCount="1085">
   <si>
     <t>Aatrox</t>
   </si>
@@ -3273,6 +3273,12 @@
   </si>
   <si>
     <t>Prestige Classic Baron</t>
+  </si>
+  <si>
+    <t>Prestige True Damage Know My Name</t>
+  </si>
+  <si>
+    <t>True Damage Know My Name</t>
   </si>
 </sst>
 </file>
@@ -3642,13 +3648,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3986,15 +3992,20 @@
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="7" width="25.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="28" style="1" customWidth="1"/>
-    <col min="9" max="12" width="25.7109375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="25.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="27.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="1" customWidth="1"/>
     <col min="13" max="13" width="30.42578125" style="1" customWidth="1"/>
-    <col min="14" max="16" width="25.7109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="27.140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="35" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.7109375" style="1" customWidth="1"/>
     <col min="17" max="17" width="27" style="1" customWidth="1"/>
     <col min="18" max="19" width="25.7109375" style="1" customWidth="1"/>
     <col min="20" max="20" width="30.7109375" style="1" customWidth="1"/>
     <col min="21" max="21" width="29.140625" style="1" customWidth="1"/>
     <col min="22" max="22" width="30.5703125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="25.7109375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="27" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.7109375" style="1" customWidth="1"/>
     <col min="25" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
@@ -4050,24 +4061,24 @@
       <c r="A4" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="38"/>
       <c r="S4" s="3"/>
       <c r="T4" s="37"/>
@@ -4260,7 +4271,9 @@
       <c r="V7" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="W7" s="40"/>
+      <c r="W7" s="40" t="s">
+        <v>1084</v>
+      </c>
       <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -5475,6 +5488,9 @@
       <c r="N34" s="9" t="s">
         <v>1007</v>
       </c>
+      <c r="O34" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="T34" s="40"/>
       <c r="U34" s="40"/>
       <c r="V34" s="40"/>
@@ -7312,7 +7328,7 @@
       <c r="Q72" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R72" s="51" t="s">
+      <c r="R72" s="49" t="s">
         <v>1082</v>
       </c>
       <c r="T72" s="40"/>
@@ -8974,6 +8990,9 @@
       <c r="J107" s="9" t="s">
         <v>856</v>
       </c>
+      <c r="K107" s="40" t="s">
+        <v>1084</v>
+      </c>
       <c r="T107" s="40"/>
       <c r="U107" s="40"/>
       <c r="V107" s="40"/>
@@ -9558,6 +9577,9 @@
       <c r="M121" s="1" t="s">
         <v>1057</v>
       </c>
+      <c r="N121" s="40" t="s">
+        <v>1084</v>
+      </c>
       <c r="T121" s="40"/>
       <c r="U121" s="40"/>
       <c r="V121" s="40"/>
@@ -11652,7 +11674,9 @@
       <c r="T165" s="43" t="s">
         <v>1052</v>
       </c>
-      <c r="U165" s="40"/>
+      <c r="U165" s="40" t="s">
+        <v>1084</v>
+      </c>
       <c r="V165" s="40"/>
       <c r="W165" s="40"/>
       <c r="X165" s="2"/>
